--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_RMSEP.xlsx
@@ -1,220 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.natif\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>RMSEP_glo</t>
-  </si>
-  <si>
-    <t>LV1_RMSEP</t>
-  </si>
-  <si>
-    <t>LV2_RMSEP</t>
-  </si>
-  <si>
-    <t>LV3_RMSEP</t>
-  </si>
-  <si>
-    <t>LV4_RMSEP</t>
-  </si>
-  <si>
-    <t>LV5_RMSEP</t>
-  </si>
-  <si>
-    <t>LV6_RMSEP</t>
-  </si>
-  <si>
-    <t>LV7_RMSEP</t>
-  </si>
-  <si>
-    <t>LV8_RMSEP</t>
-  </si>
-  <si>
-    <t>LV9_RMSEP</t>
-  </si>
-  <si>
-    <t>LV10_RMSEP</t>
-  </si>
-  <si>
-    <t>LV11_RMSEP</t>
-  </si>
-  <si>
-    <t>LV12_RMSEP</t>
-  </si>
-  <si>
-    <t>LV13_RMSEP</t>
-  </si>
-  <si>
-    <t>LV14_RMSEP</t>
-  </si>
-  <si>
-    <t>LV15_RMSEP</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,13 +27,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -258,68 +52,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -361,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -393,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -428,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -604,2521 +350,2628 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="12.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>RMSEP_glo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_RMSEP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_RMSEP</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_RMSEP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_RMSEP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_RMSEP</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_RMSEP</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_RMSEP</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_RMSEP</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_RMSEP</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_RMSEP</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_RMSEP</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_RMSEP</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_RMSEP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_RMSEP</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_RMSEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>0.1007852441846326</v>
+        <v>0.1008553302131494</v>
       </c>
       <c r="C2">
-        <v>0.1146841523906033</v>
+        <v>0.1148604146349085</v>
       </c>
       <c r="D2">
-        <v>0.1170758037848568</v>
+        <v>0.1170982346407076</v>
       </c>
       <c r="E2">
-        <v>0.1169221418186755</v>
+        <v>0.1169317529166724</v>
       </c>
       <c r="F2">
-        <v>0.11625425849269259</v>
+        <v>0.1160000982886547</v>
       </c>
       <c r="G2">
-        <v>0.1172454663289501</v>
+        <v>0.116987748319196</v>
       </c>
       <c r="H2">
-        <v>0.1175171364482198</v>
+        <v>0.117251423560506</v>
       </c>
       <c r="I2">
-        <v>0.1138784991074924</v>
+        <v>0.1139004428754559</v>
       </c>
       <c r="J2">
-        <v>0.1108346653652189</v>
+        <v>0.1106991700098848</v>
       </c>
       <c r="K2">
-        <v>0.11317313907855681</v>
+        <v>0.1127464869054648</v>
       </c>
       <c r="L2">
-        <v>0.11037492607055351</v>
+        <v>0.1102562623746369</v>
       </c>
       <c r="M2">
-        <v>0.1049962779023474</v>
+        <v>0.1054083757277419</v>
       </c>
       <c r="N2">
-        <v>0.1034842796740492</v>
+        <v>0.1035771817704613</v>
       </c>
       <c r="O2">
-        <v>9.6832955297533885E-2</v>
+        <v>0.09684953339418383</v>
       </c>
       <c r="P2">
-        <v>9.0957378677747114E-2</v>
+        <v>0.09105120627700386</v>
       </c>
       <c r="Q2">
-        <v>8.8291495539481193E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
+        <v>0.08816649166567261</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>0.10388472362736351</v>
+        <v>0.1046889852578794</v>
       </c>
       <c r="C3">
-        <v>0.11313555839483939</v>
+        <v>0.1132405395908314</v>
       </c>
       <c r="D3">
-        <v>0.122365002573433</v>
+        <v>0.1226386180505925</v>
       </c>
       <c r="E3">
-        <v>0.1191814036522174</v>
+        <v>0.1191524089712133</v>
       </c>
       <c r="F3">
-        <v>0.1113032629428207</v>
+        <v>0.111249982395368</v>
       </c>
       <c r="G3">
-        <v>0.1068241066921109</v>
+        <v>0.1063620934834092</v>
       </c>
       <c r="H3">
-        <v>0.1030043356717984</v>
+        <v>0.1031517924539951</v>
       </c>
       <c r="I3">
-        <v>9.9220493571592377E-2</v>
+        <v>0.09965434767678219</v>
       </c>
       <c r="J3">
-        <v>9.7478249827449251E-2</v>
+        <v>0.09812185646522047</v>
       </c>
       <c r="K3">
-        <v>9.4225865768828257E-2</v>
+        <v>0.0951237808269354</v>
       </c>
       <c r="L3">
-        <v>9.1862464271563679E-2</v>
+        <v>0.09301315210451751</v>
       </c>
       <c r="M3">
-        <v>9.2637303716999089E-2</v>
+        <v>0.09331185467844615</v>
       </c>
       <c r="N3">
-        <v>9.2671467332134008E-2</v>
+        <v>0.09356379714924007</v>
       </c>
       <c r="O3">
-        <v>9.467397663855695E-2</v>
+        <v>0.09545159901650838</v>
       </c>
       <c r="P3">
-        <v>9.6067957606555079E-2</v>
+        <v>0.09609359084632343</v>
       </c>
       <c r="Q3">
-        <v>9.4911402479220891E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
+        <v>0.09494617393796725</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>0.1070959477420971</v>
+        <v>0.1072362495134303</v>
       </c>
       <c r="C4">
-        <v>0.1143542858978393</v>
+        <v>0.1143122190390259</v>
       </c>
       <c r="D4">
-        <v>0.11568040331189421</v>
+        <v>0.1153076252588807</v>
       </c>
       <c r="E4">
-        <v>0.1197562744555002</v>
+        <v>0.1193045173305053</v>
       </c>
       <c r="F4">
-        <v>0.120144689006955</v>
+        <v>0.1191354603808063</v>
       </c>
       <c r="G4">
-        <v>0.1230682979251639</v>
+        <v>0.1221183466730168</v>
       </c>
       <c r="H4">
-        <v>0.1168969172049269</v>
+        <v>0.1164489693260793</v>
       </c>
       <c r="I4">
-        <v>0.11215318387885061</v>
+        <v>0.1111712165036118</v>
       </c>
       <c r="J4">
-        <v>0.1095144352939833</v>
+        <v>0.108547895250518</v>
       </c>
       <c r="K4">
-        <v>0.10911820790375221</v>
+        <v>0.1084885269668619</v>
       </c>
       <c r="L4">
-        <v>0.1042414267381114</v>
+        <v>0.1044487595234193</v>
       </c>
       <c r="M4">
-        <v>9.9962846132570768E-2</v>
+        <v>0.09984785201819908</v>
       </c>
       <c r="N4">
-        <v>9.5672668279804751E-2</v>
+        <v>0.09568982722875032</v>
       </c>
       <c r="O4">
-        <v>9.3637909826237625E-2</v>
+        <v>0.09355851113328757</v>
       </c>
       <c r="P4">
-        <v>9.3435216937669305E-2</v>
+        <v>0.0933020928863198</v>
       </c>
       <c r="Q4">
-        <v>9.4672838114924759E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
+        <v>0.09437705407006804</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>9.8202717141486665E-2</v>
+        <v>0.09802731676055332</v>
       </c>
       <c r="C5">
-        <v>0.1137504014741722</v>
+        <v>0.1137771338278501</v>
       </c>
       <c r="D5">
-        <v>0.1171601953446266</v>
+        <v>0.117817984162642</v>
       </c>
       <c r="E5">
-        <v>0.1151126958484206</v>
+        <v>0.1149281393249069</v>
       </c>
       <c r="F5">
-        <v>0.1203239614730709</v>
+        <v>0.1201881694516398</v>
       </c>
       <c r="G5">
-        <v>0.1092058658568163</v>
+        <v>0.1093553314730501</v>
       </c>
       <c r="H5">
-        <v>0.10336789910994371</v>
+        <v>0.1037656995695686</v>
       </c>
       <c r="I5">
-        <v>0.1016418871774635</v>
+        <v>0.1019911391760397</v>
       </c>
       <c r="J5">
-        <v>9.7286114783863356E-2</v>
+        <v>0.09732361754928548</v>
       </c>
       <c r="K5">
-        <v>9.2083018431809549E-2</v>
+        <v>0.09239635594200372</v>
       </c>
       <c r="L5">
-        <v>9.0068609153784132E-2</v>
+        <v>0.09027850230263418</v>
       </c>
       <c r="M5">
-        <v>8.7623753979773761E-2</v>
+        <v>0.08835624352805321</v>
       </c>
       <c r="N5">
-        <v>8.7405888154798508E-2</v>
+        <v>0.0885837622222954</v>
       </c>
       <c r="O5">
-        <v>8.8955015036136023E-2</v>
+        <v>0.09051240722079214</v>
       </c>
       <c r="P5">
-        <v>9.0284534912080119E-2</v>
+        <v>0.09203276478502924</v>
       </c>
       <c r="Q5">
-        <v>9.2283353113044836E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
+        <v>0.09368309776316464</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>9.3844383434330714E-2</v>
+        <v>0.09337746042849332</v>
       </c>
       <c r="C6">
-        <v>0.11382137845294189</v>
+        <v>0.1142218325778378</v>
       </c>
       <c r="D6">
-        <v>0.1185880798091213</v>
+        <v>0.118773130771969</v>
       </c>
       <c r="E6">
-        <v>0.1158986909618737</v>
+        <v>0.1160263344959161</v>
       </c>
       <c r="F6">
-        <v>0.1177581467630146</v>
+        <v>0.1176719096807987</v>
       </c>
       <c r="G6">
-        <v>0.10537258353019301</v>
+        <v>0.1048595597549985</v>
       </c>
       <c r="H6">
-        <v>9.9777410865414917E-2</v>
+        <v>0.09907313787045703</v>
       </c>
       <c r="I6">
-        <v>9.65267175252571E-2</v>
+        <v>0.09529597331330948</v>
       </c>
       <c r="J6">
-        <v>9.1351061024972077E-2</v>
+        <v>0.09049668198820182</v>
       </c>
       <c r="K6">
-        <v>8.8250258729233005E-2</v>
+        <v>0.08753036513103654</v>
       </c>
       <c r="L6">
-        <v>8.7240436437322294E-2</v>
+        <v>0.08640637609268484</v>
       </c>
       <c r="M6">
-        <v>8.5838702350393314E-2</v>
+        <v>0.08492586891853143</v>
       </c>
       <c r="N6">
-        <v>8.5239663496850901E-2</v>
+        <v>0.08496816369416788</v>
       </c>
       <c r="O6">
-        <v>8.596995412822582E-2</v>
+        <v>0.08561891835141476</v>
       </c>
       <c r="P6">
-        <v>8.5654241456469743E-2</v>
+        <v>0.08534467109291177</v>
       </c>
       <c r="Q6">
-        <v>8.728704540144161E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
+        <v>0.08677607252043086</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>0.1060778729718507</v>
+        <v>0.1064714022795334</v>
       </c>
       <c r="C7">
-        <v>0.11439813343174859</v>
+        <v>0.1146523710394368</v>
       </c>
       <c r="D7">
-        <v>0.1155070864933339</v>
+        <v>0.1159857369623651</v>
       </c>
       <c r="E7">
-        <v>0.1191431048103653</v>
+        <v>0.1196115401185697</v>
       </c>
       <c r="F7">
-        <v>0.12035946248413749</v>
+        <v>0.1209090527164597</v>
       </c>
       <c r="G7">
-        <v>0.1238403906910317</v>
+        <v>0.1241201407997516</v>
       </c>
       <c r="H7">
-        <v>0.1213154181246095</v>
+        <v>0.1217342512298871</v>
       </c>
       <c r="I7">
-        <v>0.1147813785165246</v>
+        <v>0.1152804906214999</v>
       </c>
       <c r="J7">
-        <v>0.1102593328909643</v>
+        <v>0.1101714141491665</v>
       </c>
       <c r="K7">
-        <v>0.1084115834942336</v>
+        <v>0.1085314306155861</v>
       </c>
       <c r="L7">
-        <v>0.1071512351625723</v>
+        <v>0.1075095049985089</v>
       </c>
       <c r="M7">
-        <v>0.1012830127550698</v>
+        <v>0.1021525334426141</v>
       </c>
       <c r="N7">
-        <v>9.6596967733343198E-2</v>
+        <v>0.09742549030221816</v>
       </c>
       <c r="O7">
-        <v>9.3442647531230022E-2</v>
+        <v>0.09417967207526221</v>
       </c>
       <c r="P7">
-        <v>9.2050844618911026E-2</v>
+        <v>0.09226052607390398</v>
       </c>
       <c r="Q7">
-        <v>9.1648187144715371E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
+        <v>0.09192515196000556</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>0.1016671681074518</v>
+        <v>0.1026903328296164</v>
       </c>
       <c r="C8">
-        <v>0.1142435696664668</v>
+        <v>0.1142447188674363</v>
       </c>
       <c r="D8">
-        <v>0.115965942795311</v>
+        <v>0.1158193611373985</v>
       </c>
       <c r="E8">
-        <v>0.12006101125516649</v>
+        <v>0.1195905055557177</v>
       </c>
       <c r="F8">
-        <v>0.122032369546426</v>
+        <v>0.1217796573240957</v>
       </c>
       <c r="G8">
-        <v>0.11886462690733859</v>
+        <v>0.1182598618590907</v>
       </c>
       <c r="H8">
-        <v>0.1124113213305931</v>
+        <v>0.1125589859569435</v>
       </c>
       <c r="I8">
-        <v>0.111469432410227</v>
+        <v>0.1117627666731298</v>
       </c>
       <c r="J8">
-        <v>0.1057449851182502</v>
+        <v>0.1057672021856223</v>
       </c>
       <c r="K8">
-        <v>0.10290635652223069</v>
+        <v>0.1034922956126765</v>
       </c>
       <c r="L8">
-        <v>9.5710379688392716E-2</v>
+        <v>0.09591984596272003</v>
       </c>
       <c r="M8">
-        <v>9.5150872891888671E-2</v>
+        <v>0.09457566258930834</v>
       </c>
       <c r="N8">
-        <v>9.1666935869495925E-2</v>
+        <v>0.09151310381792925</v>
       </c>
       <c r="O8">
-        <v>8.9774831214949849E-2</v>
+        <v>0.0898381597586549</v>
       </c>
       <c r="P8">
-        <v>8.9872083085247231E-2</v>
+        <v>0.0898293153032962</v>
       </c>
       <c r="Q8">
-        <v>9.0783752018413474E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
+        <v>0.09102746654555571</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>9.8826563426016992E-2</v>
+        <v>0.09784703362082235</v>
       </c>
       <c r="C9">
-        <v>0.1140819783025576</v>
+        <v>0.1139401661812223</v>
       </c>
       <c r="D9">
-        <v>0.11559716030954199</v>
+        <v>0.115581047819384</v>
       </c>
       <c r="E9">
-        <v>0.1191101163555322</v>
+        <v>0.1191967450099261</v>
       </c>
       <c r="F9">
-        <v>0.12047306090332301</v>
+        <v>0.1204414279659199</v>
       </c>
       <c r="G9">
-        <v>0.1177089886807407</v>
+        <v>0.1178147596679511</v>
       </c>
       <c r="H9">
-        <v>0.1120448881628243</v>
+        <v>0.1120573715190038</v>
       </c>
       <c r="I9">
-        <v>0.11159345331491199</v>
+        <v>0.1112034872923437</v>
       </c>
       <c r="J9">
-        <v>0.1058214794292479</v>
+        <v>0.1055007380943934</v>
       </c>
       <c r="K9">
-        <v>0.1037922632491227</v>
+        <v>0.1036533682937286</v>
       </c>
       <c r="L9">
-        <v>9.437509743178904E-2</v>
+        <v>0.09394670086247842</v>
       </c>
       <c r="M9">
-        <v>9.4631796774849009E-2</v>
+        <v>0.09418274530936578</v>
       </c>
       <c r="N9">
-        <v>9.150147854102185E-2</v>
+        <v>0.09116753304325094</v>
       </c>
       <c r="O9">
-        <v>8.9606655897911558E-2</v>
+        <v>0.0891495471975343</v>
       </c>
       <c r="P9">
-        <v>8.967601598224928E-2</v>
+        <v>0.08961729606372021</v>
       </c>
       <c r="Q9">
-        <v>8.9772508083163172E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
+        <v>0.08969607854386762</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>0.1003973835700952</v>
+        <v>0.09965230724602493</v>
       </c>
       <c r="C10">
-        <v>0.1143210421068621</v>
+        <v>0.1143951684038228</v>
       </c>
       <c r="D10">
-        <v>0.11598159600836221</v>
+        <v>0.1157742410266587</v>
       </c>
       <c r="E10">
-        <v>0.1194575279785841</v>
+        <v>0.1192917647814444</v>
       </c>
       <c r="F10">
-        <v>0.12126015602368929</v>
+        <v>0.1209811391446332</v>
       </c>
       <c r="G10">
-        <v>0.11862204075208881</v>
+        <v>0.1181640244835191</v>
       </c>
       <c r="H10">
-        <v>0.1125748396095544</v>
+        <v>0.1127232403465558</v>
       </c>
       <c r="I10">
-        <v>0.1119553451952631</v>
+        <v>0.1114836332365461</v>
       </c>
       <c r="J10">
-        <v>0.10579080955203531</v>
+        <v>0.1061330557833374</v>
       </c>
       <c r="K10">
-        <v>0.104423799557393</v>
+        <v>0.1045201625538991</v>
       </c>
       <c r="L10">
-        <v>9.4813671633118046E-2</v>
+        <v>0.09414557968090678</v>
       </c>
       <c r="M10">
-        <v>9.5568347459943831E-2</v>
+        <v>0.09535643733177425</v>
       </c>
       <c r="N10">
-        <v>9.2845152116452598E-2</v>
+        <v>0.09234631433074821</v>
       </c>
       <c r="O10">
-        <v>9.1172692719770659E-2</v>
+        <v>0.09009019957148542</v>
       </c>
       <c r="P10">
-        <v>9.1323022256321079E-2</v>
+        <v>0.09074325822736887</v>
       </c>
       <c r="Q10">
-        <v>9.1257390535347191E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
+        <v>0.09056572964223729</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>9.8095935806904233E-2</v>
+        <v>0.09812794132718639</v>
       </c>
       <c r="C11">
-        <v>0.1141540800172146</v>
+        <v>0.1141392543708036</v>
       </c>
       <c r="D11">
-        <v>0.115684606022091</v>
+        <v>0.1158029066379898</v>
       </c>
       <c r="E11">
-        <v>0.11938956485100589</v>
+        <v>0.1196165947335094</v>
       </c>
       <c r="F11">
-        <v>0.1205192835750651</v>
+        <v>0.121517774959299</v>
       </c>
       <c r="G11">
-        <v>0.1183671632364405</v>
+        <v>0.1187850781913221</v>
       </c>
       <c r="H11">
-        <v>0.11258180883255819</v>
+        <v>0.1125795030429857</v>
       </c>
       <c r="I11">
-        <v>0.11223161145348121</v>
+        <v>0.1122529890821305</v>
       </c>
       <c r="J11">
-        <v>0.1062480530590889</v>
+        <v>0.1060168136027071</v>
       </c>
       <c r="K11">
-        <v>0.10445916424857909</v>
+        <v>0.1041035149728257</v>
       </c>
       <c r="L11">
-        <v>9.43821234143499E-2</v>
+        <v>0.0942192479157548</v>
       </c>
       <c r="M11">
-        <v>9.4078109649059757E-2</v>
+        <v>0.09405831697586151</v>
       </c>
       <c r="N11">
-        <v>9.0994833779555265E-2</v>
+        <v>0.09120829940348348</v>
       </c>
       <c r="O11">
-        <v>8.9190830680720048E-2</v>
+        <v>0.0896134161092883</v>
       </c>
       <c r="P11">
-        <v>8.963962381728785E-2</v>
+        <v>0.08987802280843855</v>
       </c>
       <c r="Q11">
-        <v>8.9624536188364481E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
+        <v>0.09009603009540172</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>9.3307120637469473E-2</v>
+        <v>0.09333719583756324</v>
       </c>
       <c r="C12">
-        <v>0.114116683735554</v>
+        <v>0.113859295227354</v>
       </c>
       <c r="D12">
-        <v>0.11765650569053961</v>
+        <v>0.1178126044358169</v>
       </c>
       <c r="E12">
-        <v>0.11521846419197081</v>
+        <v>0.1149174101629243</v>
       </c>
       <c r="F12">
-        <v>0.1197623744900482</v>
+        <v>0.1204209362340379</v>
       </c>
       <c r="G12">
-        <v>0.10955844717439329</v>
+        <v>0.1104011934057718</v>
       </c>
       <c r="H12">
-        <v>0.1062389192038336</v>
+        <v>0.106610473499359</v>
       </c>
       <c r="I12">
-        <v>9.9554562443298897E-2</v>
+        <v>0.09998162384167043</v>
       </c>
       <c r="J12">
-        <v>9.2724209287451037E-2</v>
+        <v>0.09269408900617872</v>
       </c>
       <c r="K12">
-        <v>8.8562113575253384E-2</v>
+        <v>0.08845438477035161</v>
       </c>
       <c r="L12">
-        <v>8.6395993027279058E-2</v>
+        <v>0.0862757114057799</v>
       </c>
       <c r="M12">
-        <v>8.4149068549947262E-2</v>
+        <v>0.08387739224074833</v>
       </c>
       <c r="N12">
-        <v>8.3811554176758563E-2</v>
+        <v>0.08359797540672677</v>
       </c>
       <c r="O12">
-        <v>8.5338845885774714E-2</v>
+        <v>0.0849658171153138</v>
       </c>
       <c r="P12">
-        <v>8.6826058380217508E-2</v>
+        <v>0.08660235456802309</v>
       </c>
       <c r="Q12">
-        <v>8.9595860134257035E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
+        <v>0.0890381327861334</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>0.11102095748364819</v>
+        <v>0.1115737854198934</v>
       </c>
       <c r="C13">
-        <v>0.11440631530632819</v>
+        <v>0.1146497397188927</v>
       </c>
       <c r="D13">
-        <v>0.1219258112747079</v>
+        <v>0.1220641770510646</v>
       </c>
       <c r="E13">
-        <v>0.1183609949262442</v>
+        <v>0.1178339939786226</v>
       </c>
       <c r="F13">
-        <v>0.1208954473764008</v>
+        <v>0.1206959848063127</v>
       </c>
       <c r="G13">
-        <v>0.1207531858912988</v>
+        <v>0.1201374393495269</v>
       </c>
       <c r="H13">
-        <v>0.11325473186351891</v>
+        <v>0.1123553649780053</v>
       </c>
       <c r="I13">
-        <v>0.1126633825492529</v>
+        <v>0.1121188895364498</v>
       </c>
       <c r="J13">
-        <v>0.1098940906433389</v>
+        <v>0.109250621561389</v>
       </c>
       <c r="K13">
-        <v>0.1048215022705896</v>
+        <v>0.104982227788281</v>
       </c>
       <c r="L13">
-        <v>0.10008238476912561</v>
+        <v>0.1000820686410758</v>
       </c>
       <c r="M13">
-        <v>9.9350275383133652E-2</v>
+        <v>0.09951019038676477</v>
       </c>
       <c r="N13">
-        <v>9.7465260912756563E-2</v>
+        <v>0.09804455430394714</v>
       </c>
       <c r="O13">
-        <v>9.7284852161321086E-2</v>
+        <v>0.09766106511851448</v>
       </c>
       <c r="P13">
-        <v>9.5959843745842349E-2</v>
+        <v>0.09654921225128472</v>
       </c>
       <c r="Q13">
-        <v>9.6703940962184043E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>29</v>
+        <v>0.09699121621489779</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>9.8251664353223217E-2</v>
+        <v>0.09832897330351022</v>
       </c>
       <c r="C14">
-        <v>0.11455378702015891</v>
+        <v>0.1145985723973141</v>
       </c>
       <c r="D14">
-        <v>0.1157391482638102</v>
+        <v>0.1157839546553528</v>
       </c>
       <c r="E14">
-        <v>0.11919096386765431</v>
+        <v>0.1193022338305206</v>
       </c>
       <c r="F14">
-        <v>0.1200272091857255</v>
+        <v>0.1201870206567432</v>
       </c>
       <c r="G14">
-        <v>0.12295669329165559</v>
+        <v>0.1235314530640766</v>
       </c>
       <c r="H14">
-        <v>0.12076264979664419</v>
+        <v>0.121006869383405</v>
       </c>
       <c r="I14">
-        <v>0.1147652574849047</v>
+        <v>0.1154767797286884</v>
       </c>
       <c r="J14">
-        <v>0.1101431340505676</v>
+        <v>0.1103645337276024</v>
       </c>
       <c r="K14">
-        <v>0.1085698782537209</v>
+        <v>0.1092793946425171</v>
       </c>
       <c r="L14">
-        <v>0.107184850980051</v>
+        <v>0.1074919584130512</v>
       </c>
       <c r="M14">
-        <v>0.1009368367242337</v>
+        <v>0.1012022602192773</v>
       </c>
       <c r="N14">
-        <v>9.3615503934523309E-2</v>
+        <v>0.09387695055437624</v>
       </c>
       <c r="O14">
-        <v>9.1159233344896562E-2</v>
+        <v>0.09162326996667576</v>
       </c>
       <c r="P14">
-        <v>8.8896631383542049E-2</v>
+        <v>0.08962604189544385</v>
       </c>
       <c r="Q14">
-        <v>8.7450619202832397E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>30</v>
+        <v>0.08780906426552083</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>0.1030101086770308</v>
+        <v>0.1021894740604738</v>
       </c>
       <c r="C15">
-        <v>0.1146650359790031</v>
+        <v>0.1147969043620214</v>
       </c>
       <c r="D15">
-        <v>0.1158233159500712</v>
+        <v>0.1159950275213867</v>
       </c>
       <c r="E15">
-        <v>0.1194354848122107</v>
+        <v>0.1194674141565047</v>
       </c>
       <c r="F15">
-        <v>0.12027126191208851</v>
+        <v>0.1202963228792437</v>
       </c>
       <c r="G15">
-        <v>0.12354097375035571</v>
+        <v>0.1236396897874191</v>
       </c>
       <c r="H15">
-        <v>0.1210903361062009</v>
+        <v>0.1213939713429814</v>
       </c>
       <c r="I15">
-        <v>0.1155433011863192</v>
+        <v>0.1154550731523937</v>
       </c>
       <c r="J15">
-        <v>0.11125811471492821</v>
+        <v>0.1114146341693586</v>
       </c>
       <c r="K15">
-        <v>0.109407906478101</v>
+        <v>0.1098954880309775</v>
       </c>
       <c r="L15">
-        <v>0.108464558238329</v>
+        <v>0.1081489880354842</v>
       </c>
       <c r="M15">
-        <v>0.1030317611890081</v>
+        <v>0.1024993754235933</v>
       </c>
       <c r="N15">
-        <v>9.5958311778605795E-2</v>
+        <v>0.09601307801335729</v>
       </c>
       <c r="O15">
-        <v>9.3182544068422968E-2</v>
+        <v>0.09333309630068139</v>
       </c>
       <c r="P15">
-        <v>9.1278971337206569E-2</v>
+        <v>0.09178728915866721</v>
       </c>
       <c r="Q15">
-        <v>9.0062908241663714E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>31</v>
+        <v>0.09015518534974172</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>0.1015721125558377</v>
+        <v>0.1025780707810787</v>
       </c>
       <c r="C16">
-        <v>0.1143856393615998</v>
+        <v>0.114399253373649</v>
       </c>
       <c r="D16">
-        <v>0.115691336500227</v>
+        <v>0.1156126076037557</v>
       </c>
       <c r="E16">
-        <v>0.1194104512022108</v>
+        <v>0.1191461334149716</v>
       </c>
       <c r="F16">
-        <v>0.1206379305010839</v>
+        <v>0.1199319548343521</v>
       </c>
       <c r="G16">
-        <v>0.123875461002817</v>
+        <v>0.1229027653826355</v>
       </c>
       <c r="H16">
-        <v>0.12180182963283299</v>
+        <v>0.1211944882699032</v>
       </c>
       <c r="I16">
-        <v>0.11598121227500729</v>
+        <v>0.1159539789961084</v>
       </c>
       <c r="J16">
-        <v>0.11170419488711771</v>
+        <v>0.110982377283554</v>
       </c>
       <c r="K16">
-        <v>0.11014199130323631</v>
+        <v>0.109214430587205</v>
       </c>
       <c r="L16">
-        <v>0.1091250362950206</v>
+        <v>0.1080313721122357</v>
       </c>
       <c r="M16">
-        <v>0.1034377127564774</v>
+        <v>0.1028738836552759</v>
       </c>
       <c r="N16">
-        <v>9.6449325554313806E-2</v>
+        <v>0.09616980010385938</v>
       </c>
       <c r="O16">
-        <v>9.3748620266111415E-2</v>
+        <v>0.09299818461864431</v>
       </c>
       <c r="P16">
-        <v>9.1460506350281606E-2</v>
+        <v>0.0907158311990178</v>
       </c>
       <c r="Q16">
-        <v>8.9332532180013233E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
+        <v>0.08944301034970709</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>0.10683619392134221</v>
+        <v>0.1055647863312675</v>
       </c>
       <c r="C17">
-        <v>0.1144313067463484</v>
+        <v>0.1144687160573252</v>
       </c>
       <c r="D17">
-        <v>0.1157721774188664</v>
+        <v>0.1158086857794123</v>
       </c>
       <c r="E17">
-        <v>0.1192838441540848</v>
+        <v>0.1194436967983081</v>
       </c>
       <c r="F17">
-        <v>0.1204852009432302</v>
+        <v>0.1203854324487635</v>
       </c>
       <c r="G17">
-        <v>0.123484413485119</v>
+        <v>0.1229620637958977</v>
       </c>
       <c r="H17">
-        <v>0.1212869760905448</v>
+        <v>0.121356844663831</v>
       </c>
       <c r="I17">
-        <v>0.1158375173223057</v>
+        <v>0.1156833326043629</v>
       </c>
       <c r="J17">
-        <v>0.1113825107640649</v>
+        <v>0.1107015390539779</v>
       </c>
       <c r="K17">
-        <v>0.1103255456878519</v>
+        <v>0.1098458433352903</v>
       </c>
       <c r="L17">
-        <v>0.1094716555031474</v>
+        <v>0.1089701909563404</v>
       </c>
       <c r="M17">
-        <v>0.10460649556858199</v>
+        <v>0.1042625380539802</v>
       </c>
       <c r="N17">
-        <v>9.831282793029178E-2</v>
+        <v>0.09787817590811521</v>
       </c>
       <c r="O17">
-        <v>9.5325501269555635E-2</v>
+        <v>0.09567272765196895</v>
       </c>
       <c r="P17">
-        <v>9.2863863449575798E-2</v>
+        <v>0.09354464273074933</v>
       </c>
       <c r="Q17">
-        <v>9.1419302487275644E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>33</v>
+        <v>0.09228556010523473</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>9.3946092729635347E-2</v>
+        <v>0.09306347541575599</v>
       </c>
       <c r="C18">
-        <v>0.1139500471073516</v>
+        <v>0.113783384720047</v>
       </c>
       <c r="D18">
-        <v>0.1176254011804803</v>
+        <v>0.1180301688576798</v>
       </c>
       <c r="E18">
-        <v>0.1155153766250807</v>
+        <v>0.1150566624509778</v>
       </c>
       <c r="F18">
-        <v>0.1205498899823533</v>
+        <v>0.1207297406558862</v>
       </c>
       <c r="G18">
-        <v>0.1090644149943628</v>
+        <v>0.1083627703107927</v>
       </c>
       <c r="H18">
-        <v>0.1044264622071697</v>
+        <v>0.1037897093632704</v>
       </c>
       <c r="I18">
-        <v>9.9439734495422108E-2</v>
+        <v>0.0990552475986099</v>
       </c>
       <c r="J18">
-        <v>9.343921070327868E-2</v>
+        <v>0.09319170000056436</v>
       </c>
       <c r="K18">
-        <v>8.8889950027827971E-2</v>
+        <v>0.08880908045211544</v>
       </c>
       <c r="L18">
-        <v>8.7147755283315531E-2</v>
+        <v>0.08743005151559473</v>
       </c>
       <c r="M18">
-        <v>8.5672452947400307E-2</v>
+        <v>0.08558215859473267</v>
       </c>
       <c r="N18">
-        <v>8.5360315312153559E-2</v>
+        <v>0.08498124328153593</v>
       </c>
       <c r="O18">
-        <v>8.7074525781812434E-2</v>
+        <v>0.08703437180086908</v>
       </c>
       <c r="P18">
-        <v>8.8535052249926305E-2</v>
+        <v>0.08863730682107365</v>
       </c>
       <c r="Q18">
-        <v>8.9906563005318949E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>34</v>
+        <v>0.09012103274119386</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>9.2205162352412592E-2</v>
+        <v>0.09283043836235727</v>
       </c>
       <c r="C19">
-        <v>0.1141159410436592</v>
+        <v>0.1140164254494748</v>
       </c>
       <c r="D19">
-        <v>0.1191910890864282</v>
+        <v>0.1194596413713032</v>
       </c>
       <c r="E19">
-        <v>0.11712986003521141</v>
+        <v>0.1172275074736696</v>
       </c>
       <c r="F19">
-        <v>0.1191306951537477</v>
+        <v>0.1199083427545585</v>
       </c>
       <c r="G19">
-        <v>0.1048783352241944</v>
+        <v>0.1055033381627877</v>
       </c>
       <c r="H19">
-        <v>9.9824913774196278E-2</v>
+        <v>0.1003660114638331</v>
       </c>
       <c r="I19">
-        <v>9.5445378828968114E-2</v>
+        <v>0.09563411432334305</v>
       </c>
       <c r="J19">
-        <v>8.9942300934570577E-2</v>
+        <v>0.09020499343038692</v>
       </c>
       <c r="K19">
-        <v>8.6273006373562555E-2</v>
+        <v>0.08693601223011209</v>
       </c>
       <c r="L19">
-        <v>8.5412510564280439E-2</v>
-      </c>
-      <c r="M19" s="2">
-        <v>8.4058907185976597E-2</v>
+        <v>0.08600770840658936</v>
+      </c>
+      <c r="M19">
+        <v>0.08429857928115182</v>
       </c>
       <c r="N19">
-        <v>8.4118012368604445E-2</v>
+        <v>0.08408731737839993</v>
       </c>
       <c r="O19">
-        <v>8.5124048195938468E-2</v>
+        <v>0.08460194719593275</v>
       </c>
       <c r="P19">
-        <v>8.4644610681272117E-2</v>
+        <v>0.08447698848961942</v>
       </c>
       <c r="Q19">
-        <v>8.5298594696451388E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>35</v>
+        <v>0.08538591898533003</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>9.3626786506527976E-2</v>
+        <v>0.09443416405307033</v>
       </c>
       <c r="C20">
-        <v>0.1141410591712614</v>
+        <v>0.1139844448909556</v>
       </c>
       <c r="D20">
-        <v>0.1204581820539745</v>
+        <v>0.1198724881245658</v>
       </c>
       <c r="E20">
-        <v>0.1177710825853194</v>
+        <v>0.1178380125851615</v>
       </c>
       <c r="F20">
-        <v>0.11269612143303161</v>
+        <v>0.1129331599160731</v>
       </c>
       <c r="G20">
-        <v>0.10593646828250181</v>
+        <v>0.1066865767259286</v>
       </c>
       <c r="H20">
-        <v>0.1037323795403549</v>
+        <v>0.1052042602401827</v>
       </c>
       <c r="I20">
-        <v>9.8324424376716554E-2</v>
+        <v>0.09922271976804059</v>
       </c>
       <c r="J20">
-        <v>9.3064769830020364E-2</v>
+        <v>0.09373140908560541</v>
       </c>
       <c r="K20">
-        <v>9.0398415237413807E-2</v>
+        <v>0.09091142372067187</v>
       </c>
       <c r="L20">
-        <v>8.6938695536656327E-2</v>
+        <v>0.08780350716952046</v>
       </c>
       <c r="M20">
-        <v>8.6510175926922062E-2</v>
+        <v>0.0871705932604149</v>
       </c>
       <c r="N20">
-        <v>8.6060947824111514E-2</v>
+        <v>0.08686589906845214</v>
       </c>
       <c r="O20">
-        <v>8.3075245691547131E-2</v>
+        <v>0.08398820438710765</v>
       </c>
       <c r="P20">
-        <v>8.3054502413506079E-2</v>
+        <v>0.08394994635237762</v>
       </c>
       <c r="Q20">
-        <v>8.2797521545373842E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>36</v>
+        <v>0.08424417462376754</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>0.1065280051988135</v>
+        <v>0.1070449884863395</v>
       </c>
       <c r="C21">
-        <v>0.1133445886491402</v>
+        <v>0.11323690953459</v>
       </c>
       <c r="D21">
-        <v>0.1215768904889678</v>
+        <v>0.1219183173715012</v>
       </c>
       <c r="E21">
-        <v>0.1184805171666779</v>
+        <v>0.1192022452386633</v>
       </c>
       <c r="F21">
-        <v>0.11124550010380101</v>
+        <v>0.1126705852565485</v>
       </c>
       <c r="G21">
-        <v>0.1081450311777004</v>
+        <v>0.1089494081204249</v>
       </c>
       <c r="H21">
-        <v>0.10669912992995299</v>
+        <v>0.1072507965762932</v>
       </c>
       <c r="I21">
-        <v>0.1039204562331717</v>
+        <v>0.1039979160591877</v>
       </c>
       <c r="J21">
-        <v>0.1003096470517133</v>
+        <v>0.1014670638622502</v>
       </c>
       <c r="K21">
-        <v>9.6556898773806243E-2</v>
+        <v>0.09645775326295278</v>
       </c>
       <c r="L21">
-        <v>9.3751684701291874E-2</v>
+        <v>0.09411133798576653</v>
       </c>
       <c r="M21">
-        <v>9.2757382946057898E-2</v>
+        <v>0.09304309806331378</v>
       </c>
       <c r="N21">
-        <v>9.3965549464559928E-2</v>
+        <v>0.09411734664479664</v>
       </c>
       <c r="O21">
-        <v>9.6576388238939728E-2</v>
+        <v>0.09620022821149465</v>
       </c>
       <c r="P21">
-        <v>9.8089964792820922E-2</v>
+        <v>0.09756790855864944</v>
       </c>
       <c r="Q21">
-        <v>9.760210873188653E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>37</v>
+        <v>0.09692982300868833</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>0.1109847560144341</v>
+        <v>0.1105580133811998</v>
       </c>
       <c r="C22">
-        <v>0.1130521258814621</v>
+        <v>0.1132333076900078</v>
       </c>
       <c r="D22">
-        <v>0.1214799184835969</v>
+        <v>0.1217473281203832</v>
       </c>
       <c r="E22">
-        <v>0.1182270662682524</v>
+        <v>0.1188301100165474</v>
       </c>
       <c r="F22">
-        <v>0.1114825551529107</v>
+        <v>0.1114653396482749</v>
       </c>
       <c r="G22">
-        <v>0.1081320375617017</v>
+        <v>0.1083744627515188</v>
       </c>
       <c r="H22">
-        <v>0.1070337417372129</v>
+        <v>0.1072574311489863</v>
       </c>
       <c r="I22">
-        <v>0.1053464511044733</v>
+        <v>0.1055781885505935</v>
       </c>
       <c r="J22">
-        <v>0.10381506834110719</v>
+        <v>0.1044447105260737</v>
       </c>
       <c r="K22">
-        <v>9.9586684453644381E-2</v>
+        <v>0.1002591491028318</v>
       </c>
       <c r="L22">
-        <v>9.6614426776962775E-2</v>
+        <v>0.0976135196105186</v>
       </c>
       <c r="M22">
-        <v>9.6042694073507143E-2</v>
+        <v>0.09695952974079861</v>
       </c>
       <c r="N22">
-        <v>9.5673879498523018E-2</v>
+        <v>0.09665646322507471</v>
       </c>
       <c r="O22">
-        <v>9.6744946102899243E-2</v>
+        <v>0.09784934849206987</v>
       </c>
       <c r="P22">
-        <v>9.7069877537310376E-2</v>
+        <v>0.09820807809820818</v>
       </c>
       <c r="Q22">
-        <v>9.714426511398698E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>38</v>
+        <v>0.09831258428288456</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>9.7174418087915132E-2</v>
+        <v>0.09684362501270384</v>
       </c>
       <c r="C23">
-        <v>0.1140251895826838</v>
+        <v>0.1137848386257083</v>
       </c>
       <c r="D23">
-        <v>0.1200519943520222</v>
+        <v>0.1198785222170553</v>
       </c>
       <c r="E23">
-        <v>0.1143128127577229</v>
+        <v>0.1131964548751159</v>
       </c>
       <c r="F23">
-        <v>0.1076871508056722</v>
+        <v>0.107656755679181</v>
       </c>
       <c r="G23">
-        <v>9.9329695727577536E-2</v>
+        <v>0.09890860494372473</v>
       </c>
       <c r="H23">
-        <v>9.349561388955023E-2</v>
+        <v>0.09311802979387794</v>
       </c>
       <c r="I23">
-        <v>9.1205946928088519E-2</v>
+        <v>0.09091308943169321</v>
       </c>
       <c r="J23">
-        <v>9.0059236663355968E-2</v>
+        <v>0.08970983141770532</v>
       </c>
       <c r="K23">
-        <v>8.8439775777365143E-2</v>
+        <v>0.08846085169912347</v>
       </c>
       <c r="L23">
-        <v>8.8569869004103144E-2</v>
+        <v>0.08887671051566913</v>
       </c>
       <c r="M23">
-        <v>8.8810529845137876E-2</v>
+        <v>0.08933078060253323</v>
       </c>
       <c r="N23">
-        <v>9.0103577921202979E-2</v>
+        <v>0.09043436461577081</v>
       </c>
       <c r="O23">
-        <v>9.0407920518102036E-2</v>
+        <v>0.09084556252353916</v>
       </c>
       <c r="P23">
-        <v>9.0626520723502454E-2</v>
+        <v>0.09110566352145699</v>
       </c>
       <c r="Q23">
-        <v>9.2012978823788519E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>39</v>
+        <v>0.09231037856510262</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>0.1140751575923389</v>
+        <v>0.1140094876836566</v>
       </c>
       <c r="C24">
-        <v>0.1139703500685969</v>
+        <v>0.1139851371999889</v>
       </c>
       <c r="D24">
-        <v>0.1120409066252569</v>
+        <v>0.1120433141650615</v>
       </c>
       <c r="E24">
-        <v>0.1080952329302337</v>
+        <v>0.1085524312443316</v>
       </c>
       <c r="F24">
-        <v>0.1122148461747535</v>
+        <v>0.1126378833199163</v>
       </c>
       <c r="G24">
-        <v>0.1132408966437523</v>
+        <v>0.1135871921235466</v>
       </c>
       <c r="H24">
-        <v>0.11593522094565741</v>
+        <v>0.1165065892167323</v>
       </c>
       <c r="I24">
-        <v>0.1154274826092981</v>
+        <v>0.1159752820308477</v>
       </c>
       <c r="J24">
-        <v>0.1167394790031184</v>
+        <v>0.1174026961070225</v>
       </c>
       <c r="K24">
-        <v>0.1209034185466648</v>
+        <v>0.1214429503151345</v>
       </c>
       <c r="L24">
-        <v>0.12824712974338601</v>
+        <v>0.1287407805422352</v>
       </c>
       <c r="M24">
-        <v>0.12736317928326021</v>
+        <v>0.1283554697531625</v>
       </c>
       <c r="N24">
-        <v>0.12900710663086201</v>
+        <v>0.1300328633540684</v>
       </c>
       <c r="O24">
-        <v>0.13315152205236011</v>
+        <v>0.1344962266714149</v>
       </c>
       <c r="P24">
-        <v>0.13651004977222439</v>
+        <v>0.1378675744616263</v>
       </c>
       <c r="Q24">
-        <v>0.1420881867660195</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>40</v>
+        <v>0.1427333401195671</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>0.1206984916511938</v>
+        <v>0.1202945192818771</v>
       </c>
       <c r="C25">
-        <v>0.1206984916511938</v>
+        <v>0.1202294616762405</v>
       </c>
       <c r="D25">
-        <v>0.117799833055678</v>
+        <v>0.1173006318471522</v>
       </c>
       <c r="E25">
-        <v>0.11824153967107071</v>
+        <v>0.1178437433100141</v>
       </c>
       <c r="F25">
-        <v>0.1168154168954844</v>
+        <v>0.1166909608931947</v>
       </c>
       <c r="G25">
-        <v>0.1201807906815142</v>
+        <v>0.1194973291247244</v>
       </c>
       <c r="H25">
-        <v>0.12390060076242899</v>
+        <v>0.1230838403102879</v>
       </c>
       <c r="I25">
-        <v>0.1235390737277824</v>
+        <v>0.1230912773716061</v>
       </c>
       <c r="J25">
-        <v>0.12122830604929399</v>
+        <v>0.1209882356555728</v>
       </c>
       <c r="K25">
-        <v>0.12303987553474061</v>
+        <v>0.123113984099442</v>
       </c>
       <c r="L25">
-        <v>0.1274287855084531</v>
+        <v>0.127847719747419</v>
       </c>
       <c r="M25">
-        <v>0.1298662291575578</v>
+        <v>0.130443396530506</v>
       </c>
       <c r="N25">
-        <v>0.1342777053665451</v>
+        <v>0.1349652666916981</v>
       </c>
       <c r="O25">
-        <v>0.13916493445826861</v>
+        <v>0.1400236219419138</v>
       </c>
       <c r="P25">
-        <v>0.14161752436551961</v>
+        <v>0.1423517129112171</v>
       </c>
       <c r="Q25">
-        <v>0.1438156825897737</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>41</v>
+        <v>0.1440512752927921</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>0.11483245611628121</v>
+        <v>0.1141510209517202</v>
       </c>
       <c r="C26">
-        <v>0.1155642455784904</v>
+        <v>0.1156461994051673</v>
       </c>
       <c r="D26">
-        <v>0.1138146236031882</v>
+        <v>0.1136760844099427</v>
       </c>
       <c r="E26">
-        <v>0.10915128941928449</v>
+        <v>0.1093677184622684</v>
       </c>
       <c r="F26">
-        <v>0.107954274914699</v>
+        <v>0.1081542772617803</v>
       </c>
       <c r="G26">
-        <v>0.10724609236189291</v>
+        <v>0.107371167766366</v>
       </c>
       <c r="H26">
-        <v>0.1047992818661532</v>
+        <v>0.1053030039967561</v>
       </c>
       <c r="I26">
-        <v>0.1039567211364992</v>
+        <v>0.1045036113738816</v>
       </c>
       <c r="J26">
-        <v>0.10440869553433201</v>
+        <v>0.1042617903624029</v>
       </c>
       <c r="K26">
-        <v>0.1019494350226591</v>
+        <v>0.1020460250546038</v>
       </c>
       <c r="L26">
-        <v>0.1004911765756394</v>
+        <v>0.1000049033405826</v>
       </c>
       <c r="M26">
-        <v>0.102200872740457</v>
+        <v>0.1019014385355694</v>
       </c>
       <c r="N26">
-        <v>0.1011708393141894</v>
+        <v>0.1007244064888336</v>
       </c>
       <c r="O26">
-        <v>0.1020450541723586</v>
+        <v>0.1023761282105658</v>
       </c>
       <c r="P26">
-        <v>0.10397419811840471</v>
+        <v>0.1037842238733799</v>
       </c>
       <c r="Q26">
-        <v>0.10373091952169081</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>42</v>
+        <v>0.1037793746389153</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>0.1151399230074498</v>
+        <v>0.116238052626392</v>
       </c>
       <c r="C27">
-        <v>0.118596674090471</v>
+        <v>0.1183288012707334</v>
       </c>
       <c r="D27">
-        <v>0.11641972607804579</v>
+        <v>0.1162547020959093</v>
       </c>
       <c r="E27">
-        <v>0.1054415632596612</v>
+        <v>0.1054312225100755</v>
       </c>
       <c r="F27">
-        <v>0.10394870322428081</v>
+        <v>0.1047905257566658</v>
       </c>
       <c r="G27">
-        <v>0.10548747478308081</v>
+        <v>0.1056186604090916</v>
       </c>
       <c r="H27">
-        <v>0.10587816780670919</v>
+        <v>0.1059894497913257</v>
       </c>
       <c r="I27">
-        <v>0.10638429763657491</v>
+        <v>0.1064762801144467</v>
       </c>
       <c r="J27">
-        <v>0.10936738086333141</v>
+        <v>0.1087958833809498</v>
       </c>
       <c r="K27">
-        <v>0.1064466071315589</v>
+        <v>0.1061101766654289</v>
       </c>
       <c r="L27">
-        <v>0.105456636839362</v>
+        <v>0.1053483303883726</v>
       </c>
       <c r="M27">
-        <v>0.1030198113445821</v>
+        <v>0.1034267783182776</v>
       </c>
       <c r="N27">
-        <v>0.10072372110679791</v>
+        <v>0.1009790686984478</v>
       </c>
       <c r="O27">
-        <v>0.1010903999692722</v>
+        <v>0.1010320278330736</v>
       </c>
       <c r="P27">
-        <v>0.1028907271480623</v>
+        <v>0.1027882093658301</v>
       </c>
       <c r="Q27">
-        <v>0.1044051869395452</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>43</v>
+        <v>0.1038551590000858</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>0.1121787605635189</v>
+        <v>0.1118439291180581</v>
       </c>
       <c r="C28">
-        <v>0.1154769253922827</v>
+        <v>0.1154267389388929</v>
       </c>
       <c r="D28">
-        <v>0.1181599044269753</v>
+        <v>0.1183140898411064</v>
       </c>
       <c r="E28">
-        <v>0.1213205399944192</v>
+        <v>0.1212059488290073</v>
       </c>
       <c r="F28">
-        <v>0.1190657742724414</v>
+        <v>0.1190978083717598</v>
       </c>
       <c r="G28">
-        <v>0.1179297462299439</v>
+        <v>0.1181615926650469</v>
       </c>
       <c r="H28">
-        <v>0.1152359192602266</v>
+        <v>0.1152019145052329</v>
       </c>
       <c r="I28">
-        <v>0.1180773820814664</v>
+        <v>0.117966770708857</v>
       </c>
       <c r="J28">
-        <v>0.115012913690313</v>
+        <v>0.1146960052509891</v>
       </c>
       <c r="K28">
-        <v>0.1068938374303668</v>
+        <v>0.1075109501681347</v>
       </c>
       <c r="L28">
-        <v>0.10061370660404351</v>
+        <v>0.1003880036585729</v>
       </c>
       <c r="M28">
-        <v>9.8469153121071976E-2</v>
+        <v>0.09829045524953356</v>
       </c>
       <c r="N28">
-        <v>9.9683659226842344E-2</v>
+        <v>0.09992608071955363</v>
       </c>
       <c r="O28">
-        <v>0.1033492933511396</v>
+        <v>0.1034379751701014</v>
       </c>
       <c r="P28">
-        <v>0.1070190659597509</v>
+        <v>0.1069224063235911</v>
       </c>
       <c r="Q28">
-        <v>0.1113282836789498</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>44</v>
+        <v>0.111660925659889</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>0.1109809374912467</v>
+        <v>0.112182964344413</v>
       </c>
       <c r="C29">
-        <v>0.1158198298155565</v>
+        <v>0.1158967097699677</v>
       </c>
       <c r="D29">
-        <v>0.1188963183536236</v>
+        <v>0.1187973228235217</v>
       </c>
       <c r="E29">
-        <v>0.1219662434507055</v>
+        <v>0.1218626384619392</v>
       </c>
       <c r="F29">
-        <v>0.11955147370260839</v>
+        <v>0.1194540305676368</v>
       </c>
       <c r="G29">
-        <v>0.11801908103516739</v>
+        <v>0.1182420281942268</v>
       </c>
       <c r="H29">
-        <v>0.11701144238800849</v>
+        <v>0.1171705618588285</v>
       </c>
       <c r="I29">
-        <v>0.1223102721834487</v>
+        <v>0.1219360608915472</v>
       </c>
       <c r="J29">
-        <v>0.119547490846941</v>
+        <v>0.1183159999067883</v>
       </c>
       <c r="K29">
-        <v>0.1145154830579824</v>
+        <v>0.1141089444544935</v>
       </c>
       <c r="L29">
-        <v>0.10206785797102259</v>
+        <v>0.102381941819309</v>
       </c>
       <c r="M29">
-        <v>0.1006154203603188</v>
+        <v>0.1004176447862033</v>
       </c>
       <c r="N29">
-        <v>9.9460187317760476E-2</v>
+        <v>0.09914551412548524</v>
       </c>
       <c r="O29">
-        <v>0.101093923120812</v>
+        <v>0.1007898034997671</v>
       </c>
       <c r="P29">
-        <v>0.10430644257321391</v>
+        <v>0.1039370982387769</v>
       </c>
       <c r="Q29">
-        <v>0.10837333324360771</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>45</v>
+        <v>0.1077534497882048</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>0.1143228276711241</v>
+        <v>0.1150990755704579</v>
       </c>
       <c r="C30">
-        <v>0.1158410310465173</v>
+        <v>0.1156924776485568</v>
       </c>
       <c r="D30">
-        <v>0.119230111423235</v>
+        <v>0.118904695344818</v>
       </c>
       <c r="E30">
-        <v>0.1201913830620872</v>
+        <v>0.119578073623398</v>
       </c>
       <c r="F30">
-        <v>0.11685723480067781</v>
+        <v>0.1163869645347033</v>
       </c>
       <c r="G30">
-        <v>0.11870403880787719</v>
+        <v>0.1189013233679165</v>
       </c>
       <c r="H30">
-        <v>0.11703862164672731</v>
+        <v>0.1169439141675783</v>
       </c>
       <c r="I30">
-        <v>0.1107781166022776</v>
+        <v>0.1114245232661569</v>
       </c>
       <c r="J30">
-        <v>0.1145083543509014</v>
+        <v>0.1147518081186082</v>
       </c>
       <c r="K30">
-        <v>0.10641058589244461</v>
+        <v>0.1070024757041417</v>
       </c>
       <c r="L30">
-        <v>0.1015206239949494</v>
+        <v>0.1016515070638637</v>
       </c>
       <c r="M30">
-        <v>0.1010251588752835</v>
+        <v>0.1005785851829374</v>
       </c>
       <c r="N30">
-        <v>0.1026564900865049</v>
+        <v>0.1017663320222195</v>
       </c>
       <c r="O30">
-        <v>0.10513598345158739</v>
+        <v>0.103963627058528</v>
       </c>
       <c r="P30">
-        <v>0.10867050627784899</v>
+        <v>0.1078250105978348</v>
       </c>
       <c r="Q30">
-        <v>0.11343078065532761</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>46</v>
+        <v>0.11268611575876</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>0.1042686689905923</v>
+        <v>0.1036086989193432</v>
       </c>
       <c r="C31">
-        <v>0.11562441322239039</v>
+        <v>0.1157199146216567</v>
       </c>
       <c r="D31">
-        <v>0.11894371504498211</v>
+        <v>0.1192847156638752</v>
       </c>
       <c r="E31">
-        <v>0.1195821794387108</v>
+        <v>0.1200404069921582</v>
       </c>
       <c r="F31">
-        <v>0.1168003373446683</v>
+        <v>0.1169556106750421</v>
       </c>
       <c r="G31">
-        <v>0.1184408084084291</v>
+        <v>0.1187906861028112</v>
       </c>
       <c r="H31">
-        <v>0.1170608866801757</v>
+        <v>0.117385534005902</v>
       </c>
       <c r="I31">
-        <v>0.1118056513804707</v>
+        <v>0.111854489729837</v>
       </c>
       <c r="J31">
-        <v>0.11464331157806359</v>
+        <v>0.1157678520378181</v>
       </c>
       <c r="K31">
-        <v>0.1085262240629648</v>
+        <v>0.1088691004283903</v>
       </c>
       <c r="L31">
-        <v>0.10095146626170839</v>
+        <v>0.1006831379409446</v>
       </c>
       <c r="M31">
-        <v>9.7250577980644362E-2</v>
+        <v>0.09687284231019021</v>
       </c>
       <c r="N31">
-        <v>9.5086671100856501E-2</v>
+        <v>0.09454640688499748</v>
       </c>
       <c r="O31">
-        <v>9.4107662711274076E-2</v>
+        <v>0.09357248116325492</v>
       </c>
       <c r="P31">
-        <v>9.6550651745005961E-2</v>
+        <v>0.09549307174008538</v>
       </c>
       <c r="Q31">
-        <v>9.6939334222257215E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>47</v>
+        <v>0.09576321471609726</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>0.1079159447355648</v>
+        <v>0.1079857491041191</v>
       </c>
       <c r="C32">
-        <v>0.1157603977132715</v>
+        <v>0.115712141868659</v>
       </c>
       <c r="D32">
-        <v>0.1189889709251974</v>
+        <v>0.1185256681425094</v>
       </c>
       <c r="E32">
-        <v>0.12162817144941709</v>
+        <v>0.1214367474405629</v>
       </c>
       <c r="F32">
-        <v>0.11955364103106619</v>
+        <v>0.1190737629743409</v>
       </c>
       <c r="G32">
-        <v>0.1182392226428336</v>
+        <v>0.1180450709216662</v>
       </c>
       <c r="H32">
-        <v>0.1172961055789614</v>
+        <v>0.1172374467054416</v>
       </c>
       <c r="I32">
-        <v>0.1206590021871121</v>
+        <v>0.1207386297098142</v>
       </c>
       <c r="J32">
-        <v>0.1190592006978481</v>
+        <v>0.1191295515257424</v>
       </c>
       <c r="K32">
-        <v>0.11539629932725159</v>
+        <v>0.1157391574079969</v>
       </c>
       <c r="L32">
-        <v>0.1037414021603501</v>
+        <v>0.1040716985785074</v>
       </c>
       <c r="M32">
-        <v>0.1006063215873121</v>
+        <v>0.100496888475318</v>
       </c>
       <c r="N32">
-        <v>9.8813181797575853E-2</v>
+        <v>0.0986618733998626</v>
       </c>
       <c r="O32">
-        <v>9.8203347965104118E-2</v>
+        <v>0.09728873123028042</v>
       </c>
       <c r="P32">
-        <v>9.7863603799169405E-2</v>
+        <v>0.09739241772465324</v>
       </c>
       <c r="Q32">
-        <v>9.834464445824774E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>48</v>
+        <v>0.09728509770970913</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>0.1054737287995722</v>
+        <v>0.1051624165606507</v>
       </c>
       <c r="C33">
-        <v>0.1158767504777421</v>
+        <v>0.1158095650188834</v>
       </c>
       <c r="D33">
-        <v>0.1189870481212566</v>
+        <v>0.1187934511595916</v>
       </c>
       <c r="E33">
-        <v>0.1218667375141867</v>
+        <v>0.1216123547131817</v>
       </c>
       <c r="F33">
-        <v>0.1194989028437138</v>
+        <v>0.1192710406002679</v>
       </c>
       <c r="G33">
-        <v>0.1181940083872334</v>
+        <v>0.1181373531826288</v>
       </c>
       <c r="H33">
-        <v>0.1171576686750216</v>
+        <v>0.1167772429822115</v>
       </c>
       <c r="I33">
-        <v>0.1209787288358678</v>
+        <v>0.1201422812660392</v>
       </c>
       <c r="J33">
-        <v>0.11891004407436891</v>
+        <v>0.1182790135749806</v>
       </c>
       <c r="K33">
-        <v>0.11551740468978459</v>
+        <v>0.1150436655784997</v>
       </c>
       <c r="L33">
-        <v>0.1034144289344192</v>
+        <v>0.1027435926916544</v>
       </c>
       <c r="M33">
-        <v>9.9963966045298808E-2</v>
+        <v>0.09957890790228215</v>
       </c>
       <c r="N33">
-        <v>9.7424383245003937E-2</v>
+        <v>0.09755586270912243</v>
       </c>
       <c r="O33">
-        <v>9.6417388992045522E-2</v>
+        <v>0.09612665651850538</v>
       </c>
       <c r="P33">
-        <v>9.5586160140007814E-2</v>
+        <v>0.09535431450386847</v>
       </c>
       <c r="Q33">
-        <v>9.5556004494922409E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>49</v>
+        <v>0.0949520320762112</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>0.1059095970866394</v>
+        <v>0.1052434209119581</v>
       </c>
       <c r="C34">
-        <v>0.1157031070766515</v>
+        <v>0.1155077947402629</v>
       </c>
       <c r="D34">
-        <v>0.1187671982528784</v>
+        <v>0.1184709610947524</v>
       </c>
       <c r="E34">
-        <v>0.1215392748467919</v>
+        <v>0.1214860685845777</v>
       </c>
       <c r="F34">
-        <v>0.1193269558156775</v>
+        <v>0.1192984766199852</v>
       </c>
       <c r="G34">
-        <v>0.1184553538809289</v>
+        <v>0.117848646817709</v>
       </c>
       <c r="H34">
-        <v>0.1171953619275007</v>
+        <v>0.1166856343788837</v>
       </c>
       <c r="I34">
-        <v>0.1206164273421535</v>
+        <v>0.1202327949039949</v>
       </c>
       <c r="J34">
-        <v>0.1190278918761567</v>
+        <v>0.1189124384912526</v>
       </c>
       <c r="K34">
-        <v>0.1158016407387039</v>
+        <v>0.1159183702962381</v>
       </c>
       <c r="L34">
-        <v>0.1039678667968664</v>
+        <v>0.1042390966912859</v>
       </c>
       <c r="M34">
-        <v>0.1007264294371062</v>
+        <v>0.1006259226093117</v>
       </c>
       <c r="N34">
-        <v>9.796698617269721E-2</v>
+        <v>0.09834603418602222</v>
       </c>
       <c r="O34">
-        <v>9.7172487255476628E-2</v>
+        <v>0.0972728615711774</v>
       </c>
       <c r="P34">
-        <v>9.6231659442149842E-2</v>
+        <v>0.09621953847857381</v>
       </c>
       <c r="Q34">
-        <v>9.6103921390673058E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>50</v>
+        <v>0.0957689058127587</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>0.1075035645803441</v>
+        <v>0.1075309586745763</v>
       </c>
       <c r="C35">
-        <v>0.1160971133280904</v>
+        <v>0.1156755190569699</v>
       </c>
       <c r="D35">
-        <v>0.1192662069773633</v>
+        <v>0.1188454893615852</v>
       </c>
       <c r="E35">
-        <v>0.1220844959919791</v>
+        <v>0.1217624422912262</v>
       </c>
       <c r="F35">
-        <v>0.1199066897806237</v>
+        <v>0.1195472632765321</v>
       </c>
       <c r="G35">
-        <v>0.1188842599321165</v>
+        <v>0.1184661806824905</v>
       </c>
       <c r="H35">
-        <v>0.1175388299162624</v>
+        <v>0.1174645873102733</v>
       </c>
       <c r="I35">
-        <v>0.12108568030923531</v>
+        <v>0.1210673408731778</v>
       </c>
       <c r="J35">
-        <v>0.119807797392936</v>
+        <v>0.1201227865939377</v>
       </c>
       <c r="K35">
-        <v>0.1174402740772186</v>
+        <v>0.117493562061928</v>
       </c>
       <c r="L35">
-        <v>0.10607307235310801</v>
+        <v>0.1065997278345096</v>
       </c>
       <c r="M35">
-        <v>0.1023633290753954</v>
+        <v>0.1025544429524453</v>
       </c>
       <c r="N35">
-        <v>0.10004430835787589</v>
+        <v>0.1001807233941542</v>
       </c>
       <c r="O35">
-        <v>9.792642110286813E-2</v>
+        <v>0.09799335232472631</v>
       </c>
       <c r="P35">
-        <v>9.6868007953618634E-2</v>
+        <v>0.09713878249541301</v>
       </c>
       <c r="Q35">
-        <v>9.5384521610434689E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>51</v>
+        <v>0.09541912979468949</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>0.10752467404766421</v>
+        <v>0.1086242922620971</v>
       </c>
       <c r="C36">
-        <v>0.115684451426048</v>
+        <v>0.1159040654289855</v>
       </c>
       <c r="D36">
-        <v>0.1187288400544039</v>
+        <v>0.119256868148777</v>
       </c>
       <c r="E36">
-        <v>0.12156876892412349</v>
+        <v>0.1219031602760272</v>
       </c>
       <c r="F36">
-        <v>0.1194183449298476</v>
+        <v>0.1194023712695145</v>
       </c>
       <c r="G36">
-        <v>0.1180356397780203</v>
+        <v>0.1185231364868593</v>
       </c>
       <c r="H36">
-        <v>0.1172261286688112</v>
+        <v>0.1175523780838365</v>
       </c>
       <c r="I36">
-        <v>0.12077929298847929</v>
+        <v>0.1216556668661609</v>
       </c>
       <c r="J36">
-        <v>0.11876946730596601</v>
+        <v>0.1191465706115753</v>
       </c>
       <c r="K36">
-        <v>0.11505634679683149</v>
+        <v>0.1156914654576128</v>
       </c>
       <c r="L36">
-        <v>0.1030329600672126</v>
+        <v>0.1030125024673381</v>
       </c>
       <c r="M36">
-        <v>9.9884690064048862E-2</v>
+        <v>0.1000805240202844</v>
       </c>
       <c r="N36">
-        <v>9.8234944730845583E-2</v>
+        <v>0.09759239996514293</v>
       </c>
       <c r="O36">
-        <v>9.7484590835871188E-2</v>
+        <v>0.09705447906015874</v>
       </c>
       <c r="P36">
-        <v>9.7970284671455618E-2</v>
+        <v>0.09781734338342866</v>
       </c>
       <c r="Q36">
-        <v>9.9235905311535824E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>52</v>
+        <v>0.09893671451472287</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>0.1076197848683505</v>
+        <v>0.1075207412446563</v>
       </c>
       <c r="C37">
-        <v>0.1154834693521683</v>
+        <v>0.1154936391058342</v>
       </c>
       <c r="D37">
-        <v>0.118449021603315</v>
+        <v>0.1183026110819424</v>
       </c>
       <c r="E37">
-        <v>0.1212415269840403</v>
+        <v>0.120996712499822</v>
       </c>
       <c r="F37">
-        <v>0.1191118839101989</v>
+        <v>0.1189129028450121</v>
       </c>
       <c r="G37">
-        <v>0.11798100194724941</v>
+        <v>0.1175392009936833</v>
       </c>
       <c r="H37">
-        <v>0.11674555188917179</v>
+        <v>0.116696098821001</v>
       </c>
       <c r="I37">
-        <v>0.1206405736706764</v>
+        <v>0.1201657849610731</v>
       </c>
       <c r="J37">
-        <v>0.1188420102218772</v>
+        <v>0.1184854087519595</v>
       </c>
       <c r="K37">
-        <v>0.1152948536196949</v>
+        <v>0.1152360650912509</v>
       </c>
       <c r="L37">
-        <v>0.10296294556095111</v>
+        <v>0.1028492483164958</v>
       </c>
       <c r="M37">
-        <v>0.1001725388927909</v>
+        <v>0.1000161705156483</v>
       </c>
       <c r="N37">
-        <v>9.7805331241867757E-2</v>
+        <v>0.09786174740668883</v>
       </c>
       <c r="O37">
-        <v>9.7750278058998843E-2</v>
+        <v>0.0976407108550446</v>
       </c>
       <c r="P37">
-        <v>9.7902737601305814E-2</v>
+        <v>0.09790689898696883</v>
       </c>
       <c r="Q37">
-        <v>9.9200537239407638E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>53</v>
+        <v>0.09910904017236238</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>0.10823192089230479</v>
+        <v>0.1076372714914676</v>
       </c>
       <c r="C38">
-        <v>0.11585526687261791</v>
+        <v>0.1157032202041617</v>
       </c>
       <c r="D38">
-        <v>0.11901076411667939</v>
+        <v>0.1186737013317057</v>
       </c>
       <c r="E38">
-        <v>0.1220224241708541</v>
+        <v>0.1213677576651504</v>
       </c>
       <c r="F38">
-        <v>0.1194733999785285</v>
+        <v>0.1187744849078506</v>
       </c>
       <c r="G38">
-        <v>0.1183243654108391</v>
+        <v>0.1176226809828683</v>
       </c>
       <c r="H38">
-        <v>0.1171251605431826</v>
+        <v>0.1164258675508077</v>
       </c>
       <c r="I38">
-        <v>0.12067569457841799</v>
+        <v>0.1195761091002873</v>
       </c>
       <c r="J38">
-        <v>0.11850078523374</v>
+        <v>0.1181775546797815</v>
       </c>
       <c r="K38">
-        <v>0.11532395678503921</v>
+        <v>0.114892887077763</v>
       </c>
       <c r="L38">
-        <v>0.1034259014208455</v>
+        <v>0.1031036846179422</v>
       </c>
       <c r="M38">
-        <v>0.1003675968195106</v>
+        <v>0.1001464656542668</v>
       </c>
       <c r="N38">
-        <v>9.8172990225660492E-2</v>
+        <v>0.09818707567278864</v>
       </c>
       <c r="O38">
-        <v>9.7866165761495441E-2</v>
+        <v>0.09742171941048061</v>
       </c>
       <c r="P38">
-        <v>9.7985378210796198E-2</v>
+        <v>0.09682474231175439</v>
       </c>
       <c r="Q38">
-        <v>9.858181404703481E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>54</v>
+        <v>0.09812160466439174</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>0.1073582449588842</v>
+        <v>0.1080998777996955</v>
       </c>
       <c r="C39">
-        <v>0.1157324536131171</v>
+        <v>0.1158204979711369</v>
       </c>
       <c r="D39">
-        <v>0.11889512365525121</v>
+        <v>0.1189115827258922</v>
       </c>
       <c r="E39">
-        <v>0.12193102873021699</v>
+        <v>0.121639982090325</v>
       </c>
       <c r="F39">
-        <v>0.1195979405054725</v>
+        <v>0.1194317317823492</v>
       </c>
       <c r="G39">
-        <v>0.1185702874163294</v>
+        <v>0.1180019852499875</v>
       </c>
       <c r="H39">
-        <v>0.11733260382978999</v>
+        <v>0.1170899777665157</v>
       </c>
       <c r="I39">
-        <v>0.121134670270773</v>
+        <v>0.1205674761974236</v>
       </c>
       <c r="J39">
-        <v>0.11928572210304859</v>
+        <v>0.1188593812894216</v>
       </c>
       <c r="K39">
-        <v>0.1163799837260788</v>
+        <v>0.1155329324297596</v>
       </c>
       <c r="L39">
-        <v>0.104812795514397</v>
+        <v>0.1037282543458348</v>
       </c>
       <c r="M39">
-        <v>0.1015130737558724</v>
+        <v>0.1009324984177762</v>
       </c>
       <c r="N39">
-        <v>9.9518999446472842E-2</v>
+        <v>0.09862472903316867</v>
       </c>
       <c r="O39">
-        <v>9.8317744577408397E-2</v>
+        <v>0.09795676707036652</v>
       </c>
       <c r="P39">
-        <v>9.7980609998649743E-2</v>
+        <v>0.09766299370552278</v>
       </c>
       <c r="Q39">
-        <v>9.8331537431650198E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>55</v>
+        <v>0.09849489385466223</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>0.1077531872353816</v>
+        <v>0.1067023461957979</v>
       </c>
       <c r="C40">
-        <v>0.1157222004100206</v>
+        <v>0.1157957218916988</v>
       </c>
       <c r="D40">
-        <v>0.1189797878667735</v>
+        <v>0.1187063293965262</v>
       </c>
       <c r="E40">
-        <v>0.1218475473637121</v>
+        <v>0.1213163181493526</v>
       </c>
       <c r="F40">
-        <v>0.1194895811448744</v>
+        <v>0.1190708733906743</v>
       </c>
       <c r="G40">
-        <v>0.118254694830078</v>
+        <v>0.1180073286520164</v>
       </c>
       <c r="H40">
-        <v>0.1169152397400067</v>
+        <v>0.116943379477371</v>
       </c>
       <c r="I40">
-        <v>0.1197797103666305</v>
+        <v>0.1202283264284908</v>
       </c>
       <c r="J40">
-        <v>0.11858443470039</v>
+        <v>0.1187869057334296</v>
       </c>
       <c r="K40">
-        <v>0.11585115012886329</v>
+        <v>0.1158213544461456</v>
       </c>
       <c r="L40">
-        <v>0.10556835508345699</v>
+        <v>0.1050159254101412</v>
       </c>
       <c r="M40">
-        <v>0.1017405743006851</v>
+        <v>0.1012902458999878</v>
       </c>
       <c r="N40">
-        <v>0.10040593698100569</v>
+        <v>0.09928645726414918</v>
       </c>
       <c r="O40">
-        <v>9.8370490865760413E-2</v>
+        <v>0.09725120252405259</v>
       </c>
       <c r="P40">
-        <v>9.7080750957874273E-2</v>
+        <v>0.09639528326119116</v>
       </c>
       <c r="Q40">
-        <v>9.5455108136460451E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>56</v>
+        <v>0.09457998683228701</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>0.1196953351520417</v>
+        <v>0.1203411726060178</v>
       </c>
       <c r="C41">
-        <v>0.1180281475099992</v>
+        <v>0.1180777265140174</v>
       </c>
       <c r="D41">
-        <v>0.1212226439921375</v>
+        <v>0.1218177429455499</v>
       </c>
       <c r="E41">
-        <v>0.11761473494903769</v>
+        <v>0.1183648666451378</v>
       </c>
       <c r="F41">
-        <v>0.113393404036269</v>
+        <v>0.1136024368931457</v>
       </c>
       <c r="G41">
-        <v>0.1165467342195096</v>
+        <v>0.1168787859025793</v>
       </c>
       <c r="H41">
-        <v>0.1136665019712423</v>
+        <v>0.1140703742606337</v>
       </c>
       <c r="I41">
-        <v>0.10781499907891059</v>
+        <v>0.1086807346558239</v>
       </c>
       <c r="J41">
-        <v>0.1059183988065351</v>
+        <v>0.1065376570574061</v>
       </c>
       <c r="K41">
-        <v>0.1065679781745479</v>
+        <v>0.1068477269564636</v>
       </c>
       <c r="L41">
-        <v>0.1066954466472303</v>
+        <v>0.1063735276996065</v>
       </c>
       <c r="M41">
-        <v>0.1074520649960536</v>
+        <v>0.1073778400511941</v>
       </c>
       <c r="N41">
-        <v>0.1101955603924643</v>
+        <v>0.1097960580325194</v>
       </c>
       <c r="O41">
-        <v>0.10877887672442819</v>
+        <v>0.108545998052558</v>
       </c>
       <c r="P41">
-        <v>0.10877784022373729</v>
+        <v>0.1083721541503955</v>
       </c>
       <c r="Q41">
-        <v>0.1088935593205157</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>57</v>
+        <v>0.1083970237198404</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>0.1037851462138468</v>
+        <v>0.1043731368526334</v>
       </c>
       <c r="C42">
-        <v>0.116702007426793</v>
+        <v>0.1165643448061762</v>
       </c>
       <c r="D42">
-        <v>0.12133621587404279</v>
+        <v>0.120941320660191</v>
       </c>
       <c r="E42">
-        <v>0.1199023135798976</v>
+        <v>0.1194952659908395</v>
       </c>
       <c r="F42">
-        <v>0.1122024547621574</v>
+        <v>0.1115326654366049</v>
       </c>
       <c r="G42">
-        <v>0.11076954124526529</v>
+        <v>0.1103555201648455</v>
       </c>
       <c r="H42">
-        <v>0.103122885162722</v>
+        <v>0.1030523656388864</v>
       </c>
       <c r="I42">
-        <v>9.4763330698297538E-2</v>
+        <v>0.09566067181443408</v>
       </c>
       <c r="J42">
-        <v>9.5384662825706984E-2</v>
+        <v>0.09578398150347799</v>
       </c>
       <c r="K42">
-        <v>9.8163226789843891E-2</v>
+        <v>0.09843937907419126</v>
       </c>
       <c r="L42">
-        <v>0.1007682237873917</v>
+        <v>0.1011826412300454</v>
       </c>
       <c r="M42">
-        <v>0.10085683461963391</v>
+        <v>0.1014551828401483</v>
       </c>
       <c r="N42">
-        <v>0.101846327676894</v>
+        <v>0.1022694446896126</v>
       </c>
       <c r="O42">
-        <v>0.10078521343483419</v>
+        <v>0.1017719779877868</v>
       </c>
       <c r="P42">
-        <v>9.9711240084046929E-2</v>
+        <v>0.1005915761860742</v>
       </c>
       <c r="Q42">
-        <v>9.9129297093241101E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>58</v>
+        <v>0.09985753212969693</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>0.10549691886244381</v>
+        <v>0.1067686256152511</v>
       </c>
       <c r="C43">
-        <v>0.1164351308461872</v>
+        <v>0.1166488210060977</v>
       </c>
       <c r="D43">
-        <v>0.12038290735908461</v>
+        <v>0.1202677963984483</v>
       </c>
       <c r="E43">
-        <v>0.1184378871328695</v>
+        <v>0.1181804758781907</v>
       </c>
       <c r="F43">
-        <v>0.11160941280160649</v>
+        <v>0.1119656350729256</v>
       </c>
       <c r="G43">
-        <v>0.1112734465530672</v>
+        <v>0.111344816316402</v>
       </c>
       <c r="H43">
-        <v>0.10530632327808991</v>
+        <v>0.1053801603033712</v>
       </c>
       <c r="I43">
-        <v>9.7151791739091428E-2</v>
+        <v>0.09715855828241755</v>
       </c>
       <c r="J43">
-        <v>9.769003060266146E-2</v>
+        <v>0.09767400811067797</v>
       </c>
       <c r="K43">
-        <v>9.6911551291314943E-2</v>
+        <v>0.0972007992426261</v>
       </c>
       <c r="L43">
-        <v>9.7099916023737312E-2</v>
+        <v>0.09779345705954656</v>
       </c>
       <c r="M43">
-        <v>9.8369083047886566E-2</v>
+        <v>0.0982825394543185</v>
       </c>
       <c r="N43">
-        <v>9.679713830300038E-2</v>
+        <v>0.09724373040824913</v>
       </c>
       <c r="O43">
-        <v>9.7969744697976743E-2</v>
+        <v>0.09797302055494858</v>
       </c>
       <c r="P43">
-        <v>9.9113713788173505E-2</v>
+        <v>0.09910735201209227</v>
       </c>
       <c r="Q43">
-        <v>9.932742656436222E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>59</v>
+        <v>0.09873463963269898</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B44">
-        <v>0.1161489718797644</v>
+        <v>0.1160694160121382</v>
       </c>
       <c r="C44">
-        <v>0.1181600651012968</v>
+        <v>0.1182821548742386</v>
       </c>
       <c r="D44">
-        <v>0.1163774457626663</v>
+        <v>0.1166236874100363</v>
       </c>
       <c r="E44">
-        <v>0.1115856760787257</v>
+        <v>0.1116838435030778</v>
       </c>
       <c r="F44">
-        <v>0.11336375981567649</v>
+        <v>0.1134066400728571</v>
       </c>
       <c r="G44">
-        <v>0.1062690209625822</v>
+        <v>0.1065550195736849</v>
       </c>
       <c r="H44">
-        <v>0.1033580297010977</v>
+        <v>0.1026289176824021</v>
       </c>
       <c r="I44">
-        <v>0.1029822639306941</v>
+        <v>0.1029874396942331</v>
       </c>
       <c r="J44">
-        <v>0.10517963111538731</v>
+        <v>0.1053076596533017</v>
       </c>
       <c r="K44">
-        <v>0.1056833378563206</v>
+        <v>0.1056041755545694</v>
       </c>
       <c r="L44">
-        <v>0.10333302488921681</v>
+        <v>0.1034159334631091</v>
       </c>
       <c r="M44">
-        <v>0.1038715888641363</v>
+        <v>0.1040668456509806</v>
       </c>
       <c r="N44">
-        <v>0.1029473480867167</v>
+        <v>0.1031884197479186</v>
       </c>
       <c r="O44">
-        <v>0.10424252700230401</v>
+        <v>0.1043110924704865</v>
       </c>
       <c r="P44">
-        <v>0.1061981716353526</v>
+        <v>0.1060469353845587</v>
       </c>
       <c r="Q44">
-        <v>0.10975495010463809</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>60</v>
+        <v>0.1092057866865437</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B45">
-        <v>0.11836380946233541</v>
+        <v>0.1184501217489028</v>
       </c>
       <c r="C45">
-        <v>0.1181653251665131</v>
+        <v>0.1182876750315514</v>
       </c>
       <c r="D45">
-        <v>0.1263026478072298</v>
+        <v>0.1270062885211053</v>
       </c>
       <c r="E45">
-        <v>0.12149841727918551</v>
+        <v>0.1219633890579051</v>
       </c>
       <c r="F45">
-        <v>0.12174044353574261</v>
+        <v>0.1216990346494259</v>
       </c>
       <c r="G45">
-        <v>0.1177043720630354</v>
+        <v>0.1178517041613216</v>
       </c>
       <c r="H45">
-        <v>0.11660628350620331</v>
+        <v>0.1166554584987256</v>
       </c>
       <c r="I45">
-        <v>0.11540549422638879</v>
+        <v>0.1155806003325335</v>
       </c>
       <c r="J45">
-        <v>0.1129065465185372</v>
+        <v>0.1130979080090069</v>
       </c>
       <c r="K45">
-        <v>0.1147741988868802</v>
+        <v>0.1145281588255732</v>
       </c>
       <c r="L45">
-        <v>0.1162654696501884</v>
+        <v>0.1162958226703595</v>
       </c>
       <c r="M45">
-        <v>0.1166573535723049</v>
+        <v>0.1160880473481839</v>
       </c>
       <c r="N45">
-        <v>0.1176616220615386</v>
+        <v>0.1172218622792674</v>
       </c>
       <c r="O45">
-        <v>0.12046719327856011</v>
+        <v>0.1200628941017145</v>
       </c>
       <c r="P45">
-        <v>0.12081786947267451</v>
+        <v>0.1205106527540746</v>
       </c>
       <c r="Q45">
-        <v>0.12153248411187439</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>61</v>
+        <v>0.1215533928498523</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B46">
-        <v>0.1065703022076215</v>
+        <v>0.1064728866010351</v>
       </c>
       <c r="C46">
-        <v>0.1129754580168494</v>
+        <v>0.1130214899866195</v>
       </c>
       <c r="D46">
-        <v>0.12742788340837899</v>
+        <v>0.1275813881540055</v>
       </c>
       <c r="E46">
-        <v>0.12057627939370651</v>
+        <v>0.1207061432456829</v>
       </c>
       <c r="F46">
-        <v>0.10869186289625569</v>
+        <v>0.1080599993306307</v>
       </c>
       <c r="G46">
-        <v>0.10466654684494051</v>
+        <v>0.1042813524143531</v>
       </c>
       <c r="H46">
-        <v>0.1012763338383853</v>
+        <v>0.1015275482094735</v>
       </c>
       <c r="I46">
-        <v>9.6320720512031277E-2</v>
+        <v>0.09619074802278288</v>
       </c>
       <c r="J46">
-        <v>9.5969858215016746E-2</v>
+        <v>0.09567860856139104</v>
       </c>
       <c r="K46">
-        <v>9.6531666671243715E-2</v>
+        <v>0.09670218654371043</v>
       </c>
       <c r="L46">
-        <v>9.4826364638454064E-2</v>
+        <v>0.0952900034761901</v>
       </c>
       <c r="M46">
-        <v>9.497943238468079E-2</v>
+        <v>0.09565254871852132</v>
       </c>
       <c r="N46">
-        <v>9.6316774267934266E-2</v>
+        <v>0.09700637706902809</v>
       </c>
       <c r="O46">
-        <v>9.6515024346280356E-2</v>
+        <v>0.09728686999769955</v>
       </c>
       <c r="P46">
-        <v>9.6667945587602222E-2</v>
+        <v>0.09727384599784435</v>
       </c>
       <c r="Q46">
-        <v>9.7653197615242285E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>62</v>
+        <v>0.0983832218414276</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B47">
-        <v>0.1070177908466721</v>
+        <v>0.1059783452784343</v>
       </c>
       <c r="C47">
-        <v>0.11561062293544069</v>
+        <v>0.1162936509344983</v>
       </c>
       <c r="D47">
-        <v>0.11798716995166331</v>
+        <v>0.1187724020639986</v>
       </c>
       <c r="E47">
-        <v>0.1128066556031371</v>
+        <v>0.1133724540150501</v>
       </c>
       <c r="F47">
-        <v>0.1106269350018274</v>
+        <v>0.1116135508120838</v>
       </c>
       <c r="G47">
-        <v>0.1018129987343247</v>
+        <v>0.1018080382300647</v>
       </c>
       <c r="H47">
-        <v>9.8313246364932036E-2</v>
+        <v>0.09885484624979204</v>
       </c>
       <c r="I47">
-        <v>9.6298192007985367E-2</v>
+        <v>0.0963308357159251</v>
       </c>
       <c r="J47">
-        <v>9.6642091944530203E-2</v>
+        <v>0.09714198790465997</v>
       </c>
       <c r="K47">
-        <v>9.8802495865833867E-2</v>
+        <v>0.09916427434897307</v>
       </c>
       <c r="L47">
-        <v>9.6699475473993338E-2</v>
+        <v>0.09701201984831469</v>
       </c>
       <c r="M47">
-        <v>9.6310358115011166E-2</v>
+        <v>0.09695021996161288</v>
       </c>
       <c r="N47">
-        <v>9.6114324586856245E-2</v>
+        <v>0.096919604555956</v>
       </c>
       <c r="O47">
-        <v>9.7465930592712177E-2</v>
+        <v>0.09833670611533028</v>
       </c>
       <c r="P47">
-        <v>9.8743471721749992E-2</v>
+        <v>0.09938011854517222</v>
       </c>
       <c r="Q47">
-        <v>9.9990433959689082E-2</v>
+        <v>0.1009401394409097</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:Q19 C21:Q47 C20:O20 Q20">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="top10" dxfId="1" priority="1" bottom="1" rank="10"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_RMSEP.xlsx
@@ -1,21 +1,211 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.natif\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+  <si>
+    <t>Pretraitement</t>
+  </si>
+  <si>
+    <t>RMSEP_glo</t>
+  </si>
+  <si>
+    <t>LV0_RMSEP</t>
+  </si>
+  <si>
+    <t>LV1_RMSEP</t>
+  </si>
+  <si>
+    <t>LV2_RMSEP</t>
+  </si>
+  <si>
+    <t>LV3_RMSEP</t>
+  </si>
+  <si>
+    <t>LV4_RMSEP</t>
+  </si>
+  <si>
+    <t>LV5_RMSEP</t>
+  </si>
+  <si>
+    <t>LV6_RMSEP</t>
+  </si>
+  <si>
+    <t>LV7_RMSEP</t>
+  </si>
+  <si>
+    <t>LV8_RMSEP</t>
+  </si>
+  <si>
+    <t>LV9_RMSEP</t>
+  </si>
+  <si>
+    <t>LV10_RMSEP</t>
+  </si>
+  <si>
+    <t>LV11_RMSEP</t>
+  </si>
+  <si>
+    <t>LV12_RMSEP</t>
+  </si>
+  <si>
+    <t>LV13_RMSEP</t>
+  </si>
+  <si>
+    <t>LV14_RMSEP</t>
+  </si>
+  <si>
+    <t>LV15_RMSEP</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1000,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(1,3,5)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,11 +253,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -109,7 +307,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -141,9 +339,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -175,6 +374,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,2628 +550,2436 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pretraitement</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>RMSEP_glo</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LV1_RMSEP</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LV2_RMSEP</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LV3_RMSEP</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>LV4_RMSEP</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LV5_RMSEP</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LV6_RMSEP</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LV7_RMSEP</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LV8_RMSEP</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>LV9_RMSEP</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>LV10_RMSEP</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>LV11_RMSEP</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>LV12_RMSEP</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>LV13_RMSEP</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>LV14_RMSEP</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>LV15_RMSEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1000,1)_snv_</t>
-        </is>
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
       </c>
       <c r="B2">
-        <v>0.1008553302131494</v>
+        <v>0.10074533524608741</v>
       </c>
       <c r="C2">
-        <v>0.1148604146349085</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D2">
-        <v>0.1170982346407076</v>
+        <v>0.11474316886067031</v>
       </c>
       <c r="E2">
-        <v>0.1169317529166724</v>
+        <v>0.1169266877764629</v>
       </c>
       <c r="F2">
-        <v>0.1160000982886547</v>
+        <v>0.11653063344658671</v>
       </c>
       <c r="G2">
-        <v>0.116987748319196</v>
+        <v>0.11571086006006751</v>
       </c>
       <c r="H2">
-        <v>0.117251423560506</v>
+        <v>0.11681831318556</v>
       </c>
       <c r="I2">
-        <v>0.1139004428754559</v>
+        <v>0.116678295857794</v>
       </c>
       <c r="J2">
-        <v>0.1106991700098848</v>
+        <v>0.11386998600773079</v>
       </c>
       <c r="K2">
-        <v>0.1127464869054648</v>
+        <v>0.11104446750009481</v>
       </c>
       <c r="L2">
-        <v>0.1102562623746369</v>
+        <v>0.112811662813421</v>
       </c>
       <c r="M2">
-        <v>0.1054083757277419</v>
+        <v>0.1098559070333642</v>
       </c>
       <c r="N2">
-        <v>0.1035771817704613</v>
+        <v>0.10496048144822941</v>
       </c>
       <c r="O2">
-        <v>0.09684953339418383</v>
+        <v>0.10339035028749891</v>
       </c>
       <c r="P2">
-        <v>0.09105120627700386</v>
+        <v>9.6294445458681141E-2</v>
       </c>
       <c r="Q2">
-        <v>0.08816649166567261</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>9.0801881004864124E-2</v>
+      </c>
+      <c r="R2">
+        <v>8.7847525000461057E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
       </c>
       <c r="B3">
-        <v>0.1046889852578794</v>
+        <v>0.10453595679114069</v>
       </c>
       <c r="C3">
-        <v>0.1132405395908314</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D3">
-        <v>0.1226386180505925</v>
+        <v>0.1131521446231661</v>
       </c>
       <c r="E3">
-        <v>0.1191524089712133</v>
+        <v>0.12176567884221549</v>
       </c>
       <c r="F3">
-        <v>0.111249982395368</v>
+        <v>0.1189970706614855</v>
       </c>
       <c r="G3">
-        <v>0.1063620934834092</v>
+        <v>0.1106268300215289</v>
       </c>
       <c r="H3">
-        <v>0.1031517924539951</v>
+        <v>0.1061831940282489</v>
       </c>
       <c r="I3">
-        <v>0.09965434767678219</v>
+        <v>0.1032535602708884</v>
       </c>
       <c r="J3">
-        <v>0.09812185646522047</v>
+        <v>9.9502270544923471E-2</v>
       </c>
       <c r="K3">
-        <v>0.0951237808269354</v>
+        <v>9.8142749979271332E-2</v>
       </c>
       <c r="L3">
-        <v>0.09301315210451751</v>
+        <v>9.5545468383762419E-2</v>
       </c>
       <c r="M3">
-        <v>0.09331185467844615</v>
+        <v>9.2757359618552804E-2</v>
       </c>
       <c r="N3">
-        <v>0.09356379714924007</v>
+        <v>9.3190697896147895E-2</v>
       </c>
       <c r="O3">
-        <v>0.09545159901650838</v>
+        <v>9.3232560747015816E-2</v>
       </c>
       <c r="P3">
-        <v>0.09609359084632343</v>
+        <v>9.4687519301892759E-2</v>
       </c>
       <c r="Q3">
-        <v>0.09494617393796725</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>9.5490615104019974E-2</v>
+      </c>
+      <c r="R3">
+        <v>9.4422978006231437E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
       </c>
       <c r="B4">
-        <v>0.1072362495134303</v>
+        <v>0.10855298964182319</v>
       </c>
       <c r="C4">
-        <v>0.1143122190390259</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D4">
-        <v>0.1153076252588807</v>
+        <v>0.1144596864574192</v>
       </c>
       <c r="E4">
-        <v>0.1193045173305053</v>
+        <v>0.115795593779492</v>
       </c>
       <c r="F4">
-        <v>0.1191354603808063</v>
+        <v>0.1195880263654209</v>
       </c>
       <c r="G4">
-        <v>0.1221183466730168</v>
+        <v>0.11969560391143989</v>
       </c>
       <c r="H4">
-        <v>0.1164489693260793</v>
+        <v>0.12284540106926591</v>
       </c>
       <c r="I4">
-        <v>0.1111712165036118</v>
+        <v>0.116796774050342</v>
       </c>
       <c r="J4">
-        <v>0.108547895250518</v>
+        <v>0.1119358299777853</v>
       </c>
       <c r="K4">
-        <v>0.1084885269668619</v>
+        <v>0.10927693259446759</v>
       </c>
       <c r="L4">
-        <v>0.1044487595234193</v>
+        <v>0.1089855084401201</v>
       </c>
       <c r="M4">
-        <v>0.09984785201819908</v>
+        <v>0.10450716160972109</v>
       </c>
       <c r="N4">
-        <v>0.09568982722875032</v>
+        <v>9.9848589494845985E-2</v>
       </c>
       <c r="O4">
-        <v>0.09355851113328757</v>
+        <v>9.5885779738673307E-2</v>
       </c>
       <c r="P4">
-        <v>0.0933020928863198</v>
+        <v>9.3751950401671058E-2</v>
       </c>
       <c r="Q4">
-        <v>0.09437705407006804</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-        </is>
+        <v>9.3455228331505255E-2</v>
+      </c>
+      <c r="R4">
+        <v>9.4896307688527248E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
       </c>
       <c r="B5">
-        <v>0.09802731676055332</v>
+        <v>9.7062919336890721E-2</v>
       </c>
       <c r="C5">
-        <v>0.1137771338278501</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D5">
-        <v>0.117817984162642</v>
+        <v>0.113982307158368</v>
       </c>
       <c r="E5">
-        <v>0.1149281393249069</v>
+        <v>0.1176838667981034</v>
       </c>
       <c r="F5">
-        <v>0.1201881694516398</v>
+        <v>0.11511055679445691</v>
       </c>
       <c r="G5">
-        <v>0.1093553314730501</v>
+        <v>0.1201458174507531</v>
       </c>
       <c r="H5">
-        <v>0.1037656995695686</v>
+        <v>0.1087954348776006</v>
       </c>
       <c r="I5">
-        <v>0.1019911391760397</v>
+        <v>0.1038899344307832</v>
       </c>
       <c r="J5">
-        <v>0.09732361754928548</v>
+        <v>0.10094363936299409</v>
       </c>
       <c r="K5">
-        <v>0.09239635594200372</v>
+        <v>9.6192312165219659E-2</v>
       </c>
       <c r="L5">
-        <v>0.09027850230263418</v>
+        <v>9.1712762439917619E-2</v>
       </c>
       <c r="M5">
-        <v>0.08835624352805321</v>
+        <v>8.9736374597275223E-2</v>
       </c>
       <c r="N5">
-        <v>0.0885837622222954</v>
+        <v>8.7520346505902596E-2</v>
       </c>
       <c r="O5">
-        <v>0.09051240722079214</v>
+        <v>8.7364072120166211E-2</v>
       </c>
       <c r="P5">
-        <v>0.09203276478502924</v>
+        <v>8.9000358946309269E-2</v>
       </c>
       <c r="Q5">
-        <v>0.09368309776316464</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-        </is>
+        <v>9.0524254449830963E-2</v>
+      </c>
+      <c r="R5">
+        <v>9.2122916023509527E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
       </c>
       <c r="B6">
-        <v>0.09337746042849332</v>
+        <v>9.535302884493238E-2</v>
       </c>
       <c r="C6">
-        <v>0.1142218325778378</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D6">
-        <v>0.118773130771969</v>
+        <v>0.11379468023501479</v>
       </c>
       <c r="E6">
-        <v>0.1160263344959161</v>
+        <v>0.11879714000245981</v>
       </c>
       <c r="F6">
-        <v>0.1176719096807987</v>
+        <v>0.1164789704772153</v>
       </c>
       <c r="G6">
-        <v>0.1048595597549985</v>
+        <v>0.1181293403683754</v>
       </c>
       <c r="H6">
-        <v>0.09907313787045703</v>
+        <v>0.1058053693551733</v>
       </c>
       <c r="I6">
-        <v>0.09529597331330948</v>
+        <v>9.9635075533225079E-2</v>
       </c>
       <c r="J6">
-        <v>0.09049668198820182</v>
+        <v>9.6645586238692294E-2</v>
       </c>
       <c r="K6">
-        <v>0.08753036513103654</v>
+        <v>9.1179225932285418E-2</v>
       </c>
       <c r="L6">
-        <v>0.08640637609268484</v>
+        <v>8.8504844149698156E-2</v>
       </c>
       <c r="M6">
-        <v>0.08492586891853143</v>
+        <v>8.7457743649174552E-2</v>
       </c>
       <c r="N6">
-        <v>0.08496816369416788</v>
+        <v>8.5956222356893958E-2</v>
       </c>
       <c r="O6">
-        <v>0.08561891835141476</v>
+        <v>8.5544788218651621E-2</v>
       </c>
       <c r="P6">
-        <v>0.08534467109291177</v>
+        <v>8.6033545636729714E-2</v>
       </c>
       <c r="Q6">
-        <v>0.08677607252043086</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>8.5662654980660197E-2</v>
+      </c>
+      <c r="R6">
+        <v>8.7319351168016313E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
       </c>
       <c r="B7">
-        <v>0.1064714022795334</v>
+        <v>0.1056711089791834</v>
       </c>
       <c r="C7">
-        <v>0.1146523710394368</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D7">
-        <v>0.1159857369623651</v>
+        <v>0.1146016142590533</v>
       </c>
       <c r="E7">
-        <v>0.1196115401185697</v>
+        <v>0.1161403595458933</v>
       </c>
       <c r="F7">
-        <v>0.1209090527164597</v>
+        <v>0.1199547054787436</v>
       </c>
       <c r="G7">
-        <v>0.1241201407997516</v>
+        <v>0.1211274474980554</v>
       </c>
       <c r="H7">
-        <v>0.1217342512298871</v>
+        <v>0.12443081762492721</v>
       </c>
       <c r="I7">
-        <v>0.1152804906214999</v>
+        <v>0.1219474260250016</v>
       </c>
       <c r="J7">
-        <v>0.1101714141491665</v>
+        <v>0.1160838357405268</v>
       </c>
       <c r="K7">
-        <v>0.1085314306155861</v>
+        <v>0.11058198576776029</v>
       </c>
       <c r="L7">
-        <v>0.1075095049985089</v>
+        <v>0.10965356109780949</v>
       </c>
       <c r="M7">
-        <v>0.1021525334426141</v>
+        <v>0.1081527745926955</v>
       </c>
       <c r="N7">
-        <v>0.09742549030221816</v>
+        <v>0.1017220960585954</v>
       </c>
       <c r="O7">
-        <v>0.09417967207526221</v>
+        <v>9.6899409251567023E-2</v>
       </c>
       <c r="P7">
-        <v>0.09226052607390398</v>
+        <v>9.3378368127338823E-2</v>
       </c>
       <c r="Q7">
-        <v>0.09192515196000556</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>9.1566403006230465E-2</v>
+      </c>
+      <c r="R7">
+        <v>9.1325267683452671E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
       </c>
       <c r="B8">
-        <v>0.1026903328296164</v>
+        <v>0.1017445451562395</v>
       </c>
       <c r="C8">
-        <v>0.1142447188674363</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D8">
-        <v>0.1158193611373985</v>
+        <v>0.11431264567133009</v>
       </c>
       <c r="E8">
-        <v>0.1195905055557177</v>
+        <v>0.1159916195215073</v>
       </c>
       <c r="F8">
-        <v>0.1217796573240957</v>
+        <v>0.1193977979402966</v>
       </c>
       <c r="G8">
-        <v>0.1182598618590907</v>
+        <v>0.1213040832062017</v>
       </c>
       <c r="H8">
-        <v>0.1125589859569435</v>
+        <v>0.1187690207101593</v>
       </c>
       <c r="I8">
-        <v>0.1117627666731298</v>
+        <v>0.11274389984410441</v>
       </c>
       <c r="J8">
-        <v>0.1057672021856223</v>
+        <v>0.1121470639365372</v>
       </c>
       <c r="K8">
-        <v>0.1034922956126765</v>
+        <v>0.106105252114838</v>
       </c>
       <c r="L8">
-        <v>0.09591984596272003</v>
+        <v>0.1035601531079402</v>
       </c>
       <c r="M8">
-        <v>0.09457566258930834</v>
+        <v>9.5885409162292198E-2</v>
       </c>
       <c r="N8">
-        <v>0.09151310381792925</v>
+        <v>9.5221230650269773E-2</v>
       </c>
       <c r="O8">
-        <v>0.0898381597586549</v>
+        <v>9.2037939106321867E-2</v>
       </c>
       <c r="P8">
-        <v>0.0898293153032962</v>
+        <v>9.0740251425464685E-2</v>
       </c>
       <c r="Q8">
-        <v>0.09102746654555571</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-        </is>
+        <v>9.0628848518383348E-2</v>
+      </c>
+      <c r="R8">
+        <v>9.1626508016745559E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
       </c>
       <c r="B9">
-        <v>0.09784703362082235</v>
+        <v>9.8111444324546895E-2</v>
       </c>
       <c r="C9">
-        <v>0.1139401661812223</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D9">
-        <v>0.115581047819384</v>
+        <v>0.1141846288863476</v>
       </c>
       <c r="E9">
-        <v>0.1191967450099261</v>
+        <v>0.11572695657856109</v>
       </c>
       <c r="F9">
-        <v>0.1204414279659199</v>
+        <v>0.1196543104283479</v>
       </c>
       <c r="G9">
-        <v>0.1178147596679511</v>
+        <v>0.12123744638550051</v>
       </c>
       <c r="H9">
-        <v>0.1120573715190038</v>
+        <v>0.11833507680793171</v>
       </c>
       <c r="I9">
-        <v>0.1112034872923437</v>
+        <v>0.11251517533704709</v>
       </c>
       <c r="J9">
-        <v>0.1055007380943934</v>
+        <v>0.1122243672333101</v>
       </c>
       <c r="K9">
-        <v>0.1036533682937286</v>
+        <v>0.1061198546991186</v>
       </c>
       <c r="L9">
-        <v>0.09394670086247842</v>
+        <v>0.1044810552169243</v>
       </c>
       <c r="M9">
-        <v>0.09418274530936578</v>
+        <v>9.4660512395434895E-2</v>
       </c>
       <c r="N9">
-        <v>0.09116753304325094</v>
+        <v>9.5273279634058947E-2</v>
       </c>
       <c r="O9">
-        <v>0.0891495471975343</v>
+        <v>9.2576185752868467E-2</v>
       </c>
       <c r="P9">
-        <v>0.08961729606372021</v>
+        <v>9.0588613012175995E-2</v>
       </c>
       <c r="Q9">
-        <v>0.08969607854386762</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-        </is>
+        <v>9.0448652851135361E-2</v>
+      </c>
+      <c r="R9">
+        <v>9.052833057521173E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>26</v>
       </c>
       <c r="B10">
-        <v>0.09965230724602493</v>
+        <v>9.9166043095581247E-2</v>
       </c>
       <c r="C10">
-        <v>0.1143951684038228</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D10">
-        <v>0.1157742410266587</v>
+        <v>0.1140906845901169</v>
       </c>
       <c r="E10">
-        <v>0.1192917647814444</v>
+        <v>0.11548756087933409</v>
       </c>
       <c r="F10">
-        <v>0.1209811391446332</v>
+        <v>0.1189450582230865</v>
       </c>
       <c r="G10">
-        <v>0.1181640244835191</v>
+        <v>0.1200335987645501</v>
       </c>
       <c r="H10">
-        <v>0.1127232403465558</v>
+        <v>0.1175056513171287</v>
       </c>
       <c r="I10">
-        <v>0.1114836332365461</v>
+        <v>0.111784532743144</v>
       </c>
       <c r="J10">
-        <v>0.1061330557833374</v>
+        <v>0.11101870529922619</v>
       </c>
       <c r="K10">
-        <v>0.1045201625538991</v>
+        <v>0.1054851247691671</v>
       </c>
       <c r="L10">
-        <v>0.09414557968090678</v>
+        <v>0.10388237120389129</v>
       </c>
       <c r="M10">
-        <v>0.09535643733177425</v>
+        <v>9.4565476934924425E-2</v>
       </c>
       <c r="N10">
-        <v>0.09234631433074821</v>
+        <v>9.4959865313171909E-2</v>
       </c>
       <c r="O10">
-        <v>0.09009019957148542</v>
+        <v>9.1993970425816363E-2</v>
       </c>
       <c r="P10">
-        <v>0.09074325822736887</v>
+        <v>9.0312700342573243E-2</v>
       </c>
       <c r="Q10">
-        <v>0.09056572964223729</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>9.069874215139756E-2</v>
+      </c>
+      <c r="R10">
+        <v>9.1038394461527505E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>27</v>
       </c>
       <c r="B11">
-        <v>0.09812794132718639</v>
+        <v>9.9736137439300307E-2</v>
       </c>
       <c r="C11">
-        <v>0.1141392543708036</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D11">
-        <v>0.1158029066379898</v>
+        <v>0.11435662979712009</v>
       </c>
       <c r="E11">
-        <v>0.1196165947335094</v>
+        <v>0.11581351251776011</v>
       </c>
       <c r="F11">
-        <v>0.121517774959299</v>
+        <v>0.1193881103059159</v>
       </c>
       <c r="G11">
-        <v>0.1187850781913221</v>
+        <v>0.1211106492782958</v>
       </c>
       <c r="H11">
-        <v>0.1125795030429857</v>
+        <v>0.11840499682282921</v>
       </c>
       <c r="I11">
-        <v>0.1122529890821305</v>
+        <v>0.1131494861317241</v>
       </c>
       <c r="J11">
-        <v>0.1060168136027071</v>
+        <v>0.1127498755102407</v>
       </c>
       <c r="K11">
-        <v>0.1041035149728257</v>
+        <v>0.10720847536031081</v>
       </c>
       <c r="L11">
-        <v>0.0942192479157548</v>
+        <v>0.1052908372314454</v>
       </c>
       <c r="M11">
-        <v>0.09405831697586151</v>
+        <v>9.5171325599797088E-2</v>
       </c>
       <c r="N11">
-        <v>0.09120829940348348</v>
+        <v>9.4962282316320965E-2</v>
       </c>
       <c r="O11">
-        <v>0.0896134161092883</v>
+        <v>9.2091196837436037E-2</v>
       </c>
       <c r="P11">
-        <v>0.08987802280843855</v>
+        <v>9.042965606573436E-2</v>
       </c>
       <c r="Q11">
-        <v>0.09009603009540172</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-        </is>
+        <v>9.0533599997859371E-2</v>
+      </c>
+      <c r="R11">
+        <v>9.0358184869832422E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>28</v>
       </c>
       <c r="B12">
-        <v>0.09333719583756324</v>
+        <v>9.3894809711328769E-2</v>
       </c>
       <c r="C12">
-        <v>0.113859295227354</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D12">
-        <v>0.1178126044358169</v>
+        <v>0.1137530238588897</v>
       </c>
       <c r="E12">
-        <v>0.1149174101629243</v>
+        <v>0.1169970902391765</v>
       </c>
       <c r="F12">
-        <v>0.1204209362340379</v>
+        <v>0.11478062600258471</v>
       </c>
       <c r="G12">
-        <v>0.1104011934057718</v>
+        <v>0.1194825833697912</v>
       </c>
       <c r="H12">
-        <v>0.106610473499359</v>
+        <v>0.1102109921657588</v>
       </c>
       <c r="I12">
-        <v>0.09998162384167043</v>
+        <v>0.1065470345773827</v>
       </c>
       <c r="J12">
-        <v>0.09269408900617872</v>
+        <v>0.1002997695152089</v>
       </c>
       <c r="K12">
-        <v>0.08845438477035161</v>
+        <v>9.3775762278168834E-2</v>
       </c>
       <c r="L12">
-        <v>0.0862757114057799</v>
+        <v>8.9569714511131937E-2</v>
       </c>
       <c r="M12">
-        <v>0.08387739224074833</v>
+        <v>8.7530192349057567E-2</v>
       </c>
       <c r="N12">
-        <v>0.08359797540672677</v>
+        <v>8.5284584402482669E-2</v>
       </c>
       <c r="O12">
-        <v>0.0849658171153138</v>
+        <v>8.4875677386903894E-2</v>
       </c>
       <c r="P12">
-        <v>0.08660235456802309</v>
+        <v>8.633783171472148E-2</v>
       </c>
       <c r="Q12">
-        <v>0.0890381327861334</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-        </is>
+        <v>8.7599277363285932E-2</v>
+      </c>
+      <c r="R12">
+        <v>9.0137947022308471E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>29</v>
       </c>
       <c r="B13">
-        <v>0.1115737854198934</v>
+        <v>0.111910177232286</v>
       </c>
       <c r="C13">
-        <v>0.1146497397188927</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D13">
-        <v>0.1220641770510646</v>
+        <v>0.1143886023057599</v>
       </c>
       <c r="E13">
-        <v>0.1178339939786226</v>
+        <v>0.12166474741867379</v>
       </c>
       <c r="F13">
-        <v>0.1206959848063127</v>
+        <v>0.11807267514169489</v>
       </c>
       <c r="G13">
-        <v>0.1201374393495269</v>
+        <v>0.12060304967898069</v>
       </c>
       <c r="H13">
-        <v>0.1123553649780053</v>
+        <v>0.1204709329421972</v>
       </c>
       <c r="I13">
-        <v>0.1121188895364498</v>
+        <v>0.1126214349096059</v>
       </c>
       <c r="J13">
-        <v>0.109250621561389</v>
+        <v>0.1120623446298214</v>
       </c>
       <c r="K13">
-        <v>0.104982227788281</v>
+        <v>0.1091852895432468</v>
       </c>
       <c r="L13">
-        <v>0.1000820686410758</v>
+        <v>0.10440339634572809</v>
       </c>
       <c r="M13">
-        <v>0.09951019038676477</v>
+        <v>9.9775174033168615E-2</v>
       </c>
       <c r="N13">
-        <v>0.09804455430394714</v>
+        <v>9.8932248350893398E-2</v>
       </c>
       <c r="O13">
-        <v>0.09766106511851448</v>
+        <v>9.7298969158670867E-2</v>
       </c>
       <c r="P13">
-        <v>0.09654921225128472</v>
+        <v>9.7188554022300838E-2</v>
       </c>
       <c r="Q13">
-        <v>0.09699121621489779</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>9.5715165456428303E-2</v>
+      </c>
+      <c r="R13">
+        <v>9.6357158171281709E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>30</v>
       </c>
       <c r="B14">
-        <v>0.09832897330351022</v>
+        <v>9.6987064940827344E-2</v>
       </c>
       <c r="C14">
-        <v>0.1145985723973141</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D14">
-        <v>0.1157839546553528</v>
+        <v>0.1144267078343895</v>
       </c>
       <c r="E14">
-        <v>0.1193022338305206</v>
+        <v>0.1158149683698908</v>
       </c>
       <c r="F14">
-        <v>0.1201870206567432</v>
+        <v>0.1194893574616282</v>
       </c>
       <c r="G14">
-        <v>0.1235314530640766</v>
+        <v>0.1207482062014273</v>
       </c>
       <c r="H14">
-        <v>0.121006869383405</v>
+        <v>0.1236745406399149</v>
       </c>
       <c r="I14">
-        <v>0.1154767797286884</v>
+        <v>0.1211824859043137</v>
       </c>
       <c r="J14">
-        <v>0.1103645337276024</v>
+        <v>0.115651071806877</v>
       </c>
       <c r="K14">
-        <v>0.1092793946425171</v>
+        <v>0.1107187579479378</v>
       </c>
       <c r="L14">
-        <v>0.1074919584130512</v>
+        <v>0.1090014999385253</v>
       </c>
       <c r="M14">
-        <v>0.1012022602192773</v>
+        <v>0.1078035761921399</v>
       </c>
       <c r="N14">
-        <v>0.09387695055437624</v>
+        <v>0.1012796082184531</v>
       </c>
       <c r="O14">
-        <v>0.09162326996667576</v>
+        <v>9.4345743105839278E-2</v>
       </c>
       <c r="P14">
-        <v>0.08962604189544385</v>
+        <v>9.1589997006349996E-2</v>
       </c>
       <c r="Q14">
-        <v>0.08780906426552083</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>8.9676759181677432E-2</v>
+      </c>
+      <c r="R14">
+        <v>8.8068545814845772E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>31</v>
       </c>
       <c r="B15">
-        <v>0.1021894740604738</v>
+        <v>0.1030630285453431</v>
       </c>
       <c r="C15">
-        <v>0.1147969043620214</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D15">
-        <v>0.1159950275213867</v>
+        <v>0.1142452868669334</v>
       </c>
       <c r="E15">
-        <v>0.1194674141565047</v>
+        <v>0.1155508234969304</v>
       </c>
       <c r="F15">
-        <v>0.1202963228792437</v>
+        <v>0.11891134785117111</v>
       </c>
       <c r="G15">
-        <v>0.1236396897874191</v>
+        <v>0.11968849616309291</v>
       </c>
       <c r="H15">
-        <v>0.1213939713429814</v>
+        <v>0.1222493882881116</v>
       </c>
       <c r="I15">
-        <v>0.1154550731523937</v>
+        <v>0.12006087624405939</v>
       </c>
       <c r="J15">
-        <v>0.1114146341693586</v>
+        <v>0.11436432906227149</v>
       </c>
       <c r="K15">
-        <v>0.1098954880309775</v>
+        <v>0.1105881207498572</v>
       </c>
       <c r="L15">
-        <v>0.1081489880354842</v>
+        <v>0.1088275624772633</v>
       </c>
       <c r="M15">
-        <v>0.1024993754235933</v>
+        <v>0.1080989505856077</v>
       </c>
       <c r="N15">
-        <v>0.09601307801335729</v>
+        <v>0.102529495640886</v>
       </c>
       <c r="O15">
-        <v>0.09333309630068139</v>
+        <v>9.5936941021150565E-2</v>
       </c>
       <c r="P15">
-        <v>0.09178728915866721</v>
+        <v>9.3373153131830255E-2</v>
       </c>
       <c r="Q15">
-        <v>0.09015518534974172</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-        </is>
+        <v>9.1772147613578062E-2</v>
+      </c>
+      <c r="R15">
+        <v>9.0444588357373262E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>32</v>
       </c>
       <c r="B16">
-        <v>0.1025780707810787</v>
+        <v>0.10256858283602741</v>
       </c>
       <c r="C16">
-        <v>0.114399253373649</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D16">
-        <v>0.1156126076037557</v>
+        <v>0.1146285380434138</v>
       </c>
       <c r="E16">
-        <v>0.1191461334149716</v>
+        <v>0.1160705047518468</v>
       </c>
       <c r="F16">
-        <v>0.1199319548343521</v>
+        <v>0.11949074223956289</v>
       </c>
       <c r="G16">
-        <v>0.1229027653826355</v>
+        <v>0.12037129298694051</v>
       </c>
       <c r="H16">
-        <v>0.1211944882699032</v>
+        <v>0.1231874685207746</v>
       </c>
       <c r="I16">
-        <v>0.1159539789961084</v>
+        <v>0.120834916541752</v>
       </c>
       <c r="J16">
-        <v>0.110982377283554</v>
+        <v>0.1151493736674036</v>
       </c>
       <c r="K16">
-        <v>0.109214430587205</v>
+        <v>0.11047961474903691</v>
       </c>
       <c r="L16">
-        <v>0.1080313721122357</v>
+        <v>0.1093115480413472</v>
       </c>
       <c r="M16">
-        <v>0.1028738836552759</v>
+        <v>0.1083910683874489</v>
       </c>
       <c r="N16">
-        <v>0.09616980010385938</v>
+        <v>0.1029550883441725</v>
       </c>
       <c r="O16">
-        <v>0.09299818461864431</v>
+        <v>9.6176197275307546E-2</v>
       </c>
       <c r="P16">
-        <v>0.0907158311990178</v>
+        <v>9.3301055971280814E-2</v>
       </c>
       <c r="Q16">
-        <v>0.08944301034970709</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>9.108487454358212E-2</v>
+      </c>
+      <c r="R16">
+        <v>8.9599496599063799E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>33</v>
       </c>
       <c r="B17">
-        <v>0.1055647863312675</v>
+        <v>0.1044141248895238</v>
       </c>
       <c r="C17">
-        <v>0.1144687160573252</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D17">
-        <v>0.1158086857794123</v>
+        <v>0.11436758860403549</v>
       </c>
       <c r="E17">
-        <v>0.1194436967983081</v>
+        <v>0.1153782311601905</v>
       </c>
       <c r="F17">
-        <v>0.1203854324487635</v>
+        <v>0.1188549850810199</v>
       </c>
       <c r="G17">
-        <v>0.1229620637958977</v>
+        <v>0.1196956215938378</v>
       </c>
       <c r="H17">
-        <v>0.121356844663831</v>
+        <v>0.1228721011455729</v>
       </c>
       <c r="I17">
-        <v>0.1156833326043629</v>
+        <v>0.12067822786357869</v>
       </c>
       <c r="J17">
-        <v>0.1107015390539779</v>
+        <v>0.1155374084033764</v>
       </c>
       <c r="K17">
-        <v>0.1098458433352903</v>
+        <v>0.1115075193515588</v>
       </c>
       <c r="L17">
-        <v>0.1089701909563404</v>
+        <v>0.10953042513970949</v>
       </c>
       <c r="M17">
-        <v>0.1042625380539802</v>
+        <v>0.1091455307285407</v>
       </c>
       <c r="N17">
-        <v>0.09787817590811521</v>
+        <v>0.10383884219683</v>
       </c>
       <c r="O17">
-        <v>0.09567272765196895</v>
+        <v>9.7721950773789007E-2</v>
       </c>
       <c r="P17">
-        <v>0.09354464273074933</v>
+        <v>9.5115325845606488E-2</v>
       </c>
       <c r="Q17">
-        <v>0.09228556010523473</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>9.3165731628396489E-2</v>
+      </c>
+      <c r="R17">
+        <v>9.1069976488499779E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>34</v>
       </c>
       <c r="B18">
-        <v>0.09306347541575599</v>
+        <v>9.3800781360275351E-2</v>
       </c>
       <c r="C18">
-        <v>0.113783384720047</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D18">
-        <v>0.1180301688576798</v>
+        <v>0.1138702089437949</v>
       </c>
       <c r="E18">
-        <v>0.1150566624509778</v>
+        <v>0.11763925155594369</v>
       </c>
       <c r="F18">
-        <v>0.1207297406558862</v>
+        <v>0.11471028799371839</v>
       </c>
       <c r="G18">
-        <v>0.1083627703107927</v>
+        <v>0.12012510016734559</v>
       </c>
       <c r="H18">
-        <v>0.1037897093632704</v>
+        <v>0.108598082510734</v>
       </c>
       <c r="I18">
-        <v>0.0990552475986099</v>
+        <v>0.1044842888734487</v>
       </c>
       <c r="J18">
-        <v>0.09319170000056436</v>
+        <v>9.9757442208756569E-2</v>
       </c>
       <c r="K18">
-        <v>0.08880908045211544</v>
+        <v>9.3761975028775424E-2</v>
       </c>
       <c r="L18">
-        <v>0.08743005151559473</v>
+        <v>8.9030145573452735E-2</v>
       </c>
       <c r="M18">
-        <v>0.08558215859473267</v>
+        <v>8.7904704598455868E-2</v>
       </c>
       <c r="N18">
-        <v>0.08498124328153593</v>
+        <v>8.6019993350362922E-2</v>
       </c>
       <c r="O18">
-        <v>0.08703437180086908</v>
+        <v>8.5669646611440886E-2</v>
       </c>
       <c r="P18">
-        <v>0.08863730682107365</v>
+        <v>8.7691339055780332E-2</v>
       </c>
       <c r="Q18">
-        <v>0.09012103274119386</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-        </is>
+        <v>8.9108681819719204E-2</v>
+      </c>
+      <c r="R18">
+        <v>9.0667365636248567E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>35</v>
       </c>
       <c r="B19">
-        <v>0.09283043836235727</v>
+        <v>9.3323429579700273E-2</v>
       </c>
       <c r="C19">
-        <v>0.1140164254494748</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D19">
-        <v>0.1194596413713032</v>
+        <v>0.1144819166563105</v>
       </c>
       <c r="E19">
-        <v>0.1172275074736696</v>
+        <v>0.11953116201897721</v>
       </c>
       <c r="F19">
-        <v>0.1199083427545585</v>
+        <v>0.1173216725618297</v>
       </c>
       <c r="G19">
-        <v>0.1055033381627877</v>
+        <v>0.1191971206640552</v>
       </c>
       <c r="H19">
-        <v>0.1003660114638331</v>
+        <v>0.1052505316439422</v>
       </c>
       <c r="I19">
-        <v>0.09563411432334305</v>
+        <v>9.9881759776950768E-2</v>
       </c>
       <c r="J19">
-        <v>0.09020499343038692</v>
+        <v>9.6182023030538008E-2</v>
       </c>
       <c r="K19">
-        <v>0.08693601223011209</v>
+        <v>9.0520517150302182E-2</v>
       </c>
       <c r="L19">
-        <v>0.08600770840658936</v>
+        <v>8.6964040643799645E-2</v>
       </c>
       <c r="M19">
-        <v>0.08429857928115182</v>
+        <v>8.6038447424794842E-2</v>
       </c>
       <c r="N19">
-        <v>0.08408731737839993</v>
+        <v>8.4042286236798519E-2</v>
       </c>
       <c r="O19">
-        <v>0.08460194719593275</v>
+        <v>8.4259970058911116E-2</v>
       </c>
       <c r="P19">
-        <v>0.08447698848961942</v>
+        <v>8.5124987991877954E-2</v>
       </c>
       <c r="Q19">
-        <v>0.08538591898533003</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>8.4607798025736605E-2</v>
+      </c>
+      <c r="R19">
+        <v>8.5224297077116568E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>36</v>
       </c>
       <c r="B20">
-        <v>0.09443416405307033</v>
+        <v>9.3626207817703755E-2</v>
       </c>
       <c r="C20">
-        <v>0.1139844448909556</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D20">
-        <v>0.1198724881245658</v>
+        <v>0.1140752258591267</v>
       </c>
       <c r="E20">
-        <v>0.1178380125851615</v>
+        <v>0.11994826136594371</v>
       </c>
       <c r="F20">
-        <v>0.1129331599160731</v>
+        <v>0.11782802566679861</v>
       </c>
       <c r="G20">
-        <v>0.1066865767259286</v>
+        <v>0.11295321590523121</v>
       </c>
       <c r="H20">
-        <v>0.1052042602401827</v>
+        <v>0.10604723911407909</v>
       </c>
       <c r="I20">
-        <v>0.09922271976804059</v>
+        <v>0.1038571668924268</v>
       </c>
       <c r="J20">
-        <v>0.09373140908560541</v>
+        <v>9.7741100025395627E-2</v>
       </c>
       <c r="K20">
-        <v>0.09091142372067187</v>
+        <v>9.2812668028109002E-2</v>
       </c>
       <c r="L20">
-        <v>0.08780350716952046</v>
+        <v>9.0320015244098217E-2</v>
       </c>
       <c r="M20">
-        <v>0.0871705932604149</v>
+        <v>8.6861345062426085E-2</v>
       </c>
       <c r="N20">
-        <v>0.08686589906845214</v>
+        <v>8.6638097199897068E-2</v>
       </c>
       <c r="O20">
-        <v>0.08398820438710765</v>
+        <v>8.6239295765171531E-2</v>
       </c>
       <c r="P20">
-        <v>0.08394994635237762</v>
+        <v>8.3552638629354498E-2</v>
       </c>
       <c r="Q20">
-        <v>0.08424417462376754</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>8.3385266925074392E-2</v>
+      </c>
+      <c r="R20">
+        <v>8.3180640462912125E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>37</v>
       </c>
       <c r="B21">
-        <v>0.1070449884863395</v>
+        <v>0.1073244677315648</v>
       </c>
       <c r="C21">
-        <v>0.11323690953459</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D21">
-        <v>0.1219183173715012</v>
+        <v>0.1132726668675908</v>
       </c>
       <c r="E21">
-        <v>0.1192022452386633</v>
+        <v>0.1222616949496951</v>
       </c>
       <c r="F21">
-        <v>0.1126705852565485</v>
+        <v>0.1193424310921215</v>
       </c>
       <c r="G21">
-        <v>0.1089494081204249</v>
+        <v>0.11255523351835971</v>
       </c>
       <c r="H21">
-        <v>0.1072507965762932</v>
+        <v>0.1085528220598722</v>
       </c>
       <c r="I21">
-        <v>0.1039979160591877</v>
+        <v>0.1067082348382434</v>
       </c>
       <c r="J21">
-        <v>0.1014670638622502</v>
+        <v>0.1036623220746072</v>
       </c>
       <c r="K21">
-        <v>0.09645775326295278</v>
+        <v>0.10041646268018201</v>
       </c>
       <c r="L21">
-        <v>0.09411133798576653</v>
+        <v>9.5967896384794277E-2</v>
       </c>
       <c r="M21">
-        <v>0.09304309806331378</v>
+        <v>9.3572588480293886E-2</v>
       </c>
       <c r="N21">
-        <v>0.09411734664479664</v>
+        <v>9.2664886527141332E-2</v>
       </c>
       <c r="O21">
-        <v>0.09620022821149465</v>
+        <v>9.3622480953009748E-2</v>
       </c>
       <c r="P21">
-        <v>0.09756790855864944</v>
+        <v>9.6167886280456652E-2</v>
       </c>
       <c r="Q21">
-        <v>0.09692982300868833</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>9.7637415047089338E-2</v>
+      </c>
+      <c r="R21">
+        <v>9.686269992161671E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>38</v>
       </c>
       <c r="B22">
-        <v>0.1105580133811998</v>
+        <v>0.1110671199427436</v>
       </c>
       <c r="C22">
-        <v>0.1132333076900078</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D22">
-        <v>0.1217473281203832</v>
+        <v>0.1133080264510096</v>
       </c>
       <c r="E22">
-        <v>0.1188301100165474</v>
+        <v>0.1217944924482075</v>
       </c>
       <c r="F22">
-        <v>0.1114653396482749</v>
+        <v>0.1189069685396308</v>
       </c>
       <c r="G22">
-        <v>0.1083744627515188</v>
+        <v>0.1120039083024003</v>
       </c>
       <c r="H22">
-        <v>0.1072574311489863</v>
+        <v>0.1090111621986905</v>
       </c>
       <c r="I22">
-        <v>0.1055781885505935</v>
+        <v>0.10751493477482529</v>
       </c>
       <c r="J22">
-        <v>0.1044447105260737</v>
+        <v>0.1060682651940424</v>
       </c>
       <c r="K22">
-        <v>0.1002591491028318</v>
+        <v>0.10485642279323169</v>
       </c>
       <c r="L22">
-        <v>0.0976135196105186</v>
+        <v>0.1003584090932378</v>
       </c>
       <c r="M22">
-        <v>0.09695952974079861</v>
+        <v>9.7670445299383762E-2</v>
       </c>
       <c r="N22">
-        <v>0.09665646322507471</v>
+        <v>9.6154246124238965E-2</v>
       </c>
       <c r="O22">
-        <v>0.09784934849206987</v>
+        <v>9.5429719543215011E-2</v>
       </c>
       <c r="P22">
-        <v>0.09820807809820818</v>
+        <v>9.6589650571664881E-2</v>
       </c>
       <c r="Q22">
-        <v>0.09831258428288456</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>9.7030291485610015E-2</v>
+      </c>
+      <c r="R22">
+        <v>9.7351786144229666E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>39</v>
       </c>
       <c r="B23">
-        <v>0.09684362501270384</v>
+        <v>9.7211614046188943E-2</v>
       </c>
       <c r="C23">
-        <v>0.1137848386257083</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D23">
-        <v>0.1198785222170553</v>
+        <v>0.1138221115894377</v>
       </c>
       <c r="E23">
-        <v>0.1131964548751159</v>
+        <v>0.1201859622228298</v>
       </c>
       <c r="F23">
-        <v>0.107656755679181</v>
+        <v>0.1139078990618235</v>
       </c>
       <c r="G23">
-        <v>0.09890860494372473</v>
+        <v>0.1077169529721041</v>
       </c>
       <c r="H23">
-        <v>0.09311802979387794</v>
+        <v>9.9595279311786314E-2</v>
       </c>
       <c r="I23">
-        <v>0.09091308943169321</v>
+        <v>9.4002170185956482E-2</v>
       </c>
       <c r="J23">
-        <v>0.08970983141770532</v>
+        <v>9.1923021968757512E-2</v>
       </c>
       <c r="K23">
-        <v>0.08846085169912347</v>
+        <v>9.0997556123549442E-2</v>
       </c>
       <c r="L23">
-        <v>0.08887671051566913</v>
+        <v>8.9362936612053315E-2</v>
       </c>
       <c r="M23">
-        <v>0.08933078060253323</v>
+        <v>8.892964299746331E-2</v>
       </c>
       <c r="N23">
-        <v>0.09043436461577081</v>
+        <v>8.8921455840010835E-2</v>
       </c>
       <c r="O23">
-        <v>0.09084556252353916</v>
+        <v>8.9721296868493797E-2</v>
       </c>
       <c r="P23">
-        <v>0.09110566352145699</v>
+        <v>9.0303617393644606E-2</v>
       </c>
       <c r="Q23">
-        <v>0.09231037856510262</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>9.013297193655756E-2</v>
+      </c>
+      <c r="R23">
+        <v>9.1667695517245421E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>40</v>
       </c>
       <c r="B24">
-        <v>0.1140094876836566</v>
+        <v>0.1119664178590343</v>
       </c>
       <c r="C24">
-        <v>0.1139851371999889</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D24">
-        <v>0.1120433141650615</v>
+        <v>0.1158906923053451</v>
       </c>
       <c r="E24">
-        <v>0.1085524312443316</v>
+        <v>0.1191369586194152</v>
       </c>
       <c r="F24">
-        <v>0.1126378833199163</v>
+        <v>0.122232122272036</v>
       </c>
       <c r="G24">
-        <v>0.1135871921235466</v>
+        <v>0.11999862843207119</v>
       </c>
       <c r="H24">
-        <v>0.1165065892167323</v>
+        <v>0.1190436530041203</v>
       </c>
       <c r="I24">
-        <v>0.1159752820308477</v>
+        <v>0.1161321866190962</v>
       </c>
       <c r="J24">
-        <v>0.1174026961070225</v>
+        <v>0.1183916088294952</v>
       </c>
       <c r="K24">
-        <v>0.1214429503151345</v>
+        <v>0.11562181786430351</v>
       </c>
       <c r="L24">
-        <v>0.1287407805422352</v>
+        <v>0.106562061394637</v>
       </c>
       <c r="M24">
-        <v>0.1283554697531625</v>
+        <v>0.1007084790493246</v>
       </c>
       <c r="N24">
-        <v>0.1300328633540684</v>
+        <v>9.8878217647735009E-2</v>
       </c>
       <c r="O24">
-        <v>0.1344962266714149</v>
+        <v>0.10018368569140609</v>
       </c>
       <c r="P24">
-        <v>0.1378675744616263</v>
+        <v>0.10407607897484041</v>
       </c>
       <c r="Q24">
-        <v>0.1427333401195671</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.1076741266939294</v>
+      </c>
+      <c r="R24">
+        <v>0.11243122878855</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>41</v>
       </c>
       <c r="B25">
-        <v>0.1202945192818771</v>
+        <v>0.1132015679960662</v>
       </c>
       <c r="C25">
-        <v>0.1202294616762405</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D25">
-        <v>0.1173006318471522</v>
+        <v>0.1157551716374307</v>
       </c>
       <c r="E25">
-        <v>0.1178437433100141</v>
+        <v>0.11885820162959811</v>
       </c>
       <c r="F25">
-        <v>0.1166909608931947</v>
+        <v>0.1219971011164744</v>
       </c>
       <c r="G25">
-        <v>0.1194973291247244</v>
+        <v>0.1194605859876218</v>
       </c>
       <c r="H25">
-        <v>0.1230838403102879</v>
+        <v>0.1183169958352572</v>
       </c>
       <c r="I25">
-        <v>0.1230912773716061</v>
+        <v>0.1173948609064845</v>
       </c>
       <c r="J25">
-        <v>0.1209882356555728</v>
+        <v>0.1226787684368148</v>
       </c>
       <c r="K25">
-        <v>0.123113984099442</v>
+        <v>0.11971061833233849</v>
       </c>
       <c r="L25">
-        <v>0.127847719747419</v>
+        <v>0.11496528251527489</v>
       </c>
       <c r="M25">
-        <v>0.130443396530506</v>
+        <v>0.1030211150046501</v>
       </c>
       <c r="N25">
-        <v>0.1349652666916981</v>
+        <v>0.1010643309472274</v>
       </c>
       <c r="O25">
-        <v>0.1400236219419138</v>
+        <v>0.10013480516784699</v>
       </c>
       <c r="P25">
-        <v>0.1423517129112171</v>
+        <v>0.1026576258311048</v>
       </c>
       <c r="Q25">
-        <v>0.1440512752927921</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.1057936171719925</v>
+      </c>
+      <c r="R25">
+        <v>0.1098643988277756</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>42</v>
       </c>
       <c r="B26">
-        <v>0.1141510209517202</v>
+        <v>0.1154603476689546</v>
       </c>
       <c r="C26">
-        <v>0.1156461994051673</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D26">
-        <v>0.1136760844099427</v>
+        <v>0.1156677329653147</v>
       </c>
       <c r="E26">
-        <v>0.1093677184622684</v>
+        <v>0.1189848434177421</v>
       </c>
       <c r="F26">
-        <v>0.1081542772617803</v>
+        <v>0.1196998444109386</v>
       </c>
       <c r="G26">
-        <v>0.107371167766366</v>
+        <v>0.11658692997545129</v>
       </c>
       <c r="H26">
-        <v>0.1053030039967561</v>
+        <v>0.1186296190077443</v>
       </c>
       <c r="I26">
-        <v>0.1045036113738816</v>
+        <v>0.1168627267040997</v>
       </c>
       <c r="J26">
-        <v>0.1042617903624029</v>
+        <v>0.1103764079203048</v>
       </c>
       <c r="K26">
-        <v>0.1020460250546038</v>
+        <v>0.11458052235400031</v>
       </c>
       <c r="L26">
-        <v>0.1000049033405826</v>
+        <v>0.106415159200897</v>
       </c>
       <c r="M26">
-        <v>0.1019014385355694</v>
+        <v>0.101082483625391</v>
       </c>
       <c r="N26">
-        <v>0.1007244064888336</v>
+        <v>0.1002243229315154</v>
       </c>
       <c r="O26">
-        <v>0.1023761282105658</v>
+        <v>0.1016414216462492</v>
       </c>
       <c r="P26">
-        <v>0.1037842238733799</v>
+        <v>0.10360679836216249</v>
       </c>
       <c r="Q26">
-        <v>0.1037793746389153</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.10717990374075501</v>
+      </c>
+      <c r="R26">
+        <v>0.1121442343515473</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>43</v>
       </c>
       <c r="B27">
-        <v>0.116238052626392</v>
+        <v>0.10307949997458581</v>
       </c>
       <c r="C27">
-        <v>0.1183288012707334</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D27">
-        <v>0.1162547020959093</v>
+        <v>0.11576278608811461</v>
       </c>
       <c r="E27">
-        <v>0.1054312225100755</v>
+        <v>0.1190606187183583</v>
       </c>
       <c r="F27">
-        <v>0.1047905257566658</v>
+        <v>0.1197440910153612</v>
       </c>
       <c r="G27">
-        <v>0.1056186604090916</v>
+        <v>0.11628815047951439</v>
       </c>
       <c r="H27">
-        <v>0.1059894497913257</v>
+        <v>0.1183924904087808</v>
       </c>
       <c r="I27">
-        <v>0.1064762801144467</v>
+        <v>0.11693460594792909</v>
       </c>
       <c r="J27">
-        <v>0.1087958833809498</v>
+        <v>0.1116254849675845</v>
       </c>
       <c r="K27">
-        <v>0.1061101766654289</v>
+        <v>0.1146294086685858</v>
       </c>
       <c r="L27">
-        <v>0.1053483303883726</v>
+        <v>0.1076377398265263</v>
       </c>
       <c r="M27">
-        <v>0.1034267783182776</v>
+        <v>9.951666724633465E-2</v>
       </c>
       <c r="N27">
-        <v>0.1009790686984478</v>
+        <v>9.6311936418000454E-2</v>
       </c>
       <c r="O27">
-        <v>0.1010320278330736</v>
+        <v>9.4161153367425976E-2</v>
       </c>
       <c r="P27">
-        <v>0.1027882093658301</v>
+        <v>9.2920641344178018E-2</v>
       </c>
       <c r="Q27">
-        <v>0.1038551590000858</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>9.4707036710045073E-2</v>
+      </c>
+      <c r="R27">
+        <v>9.5152383755237116E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>44</v>
       </c>
       <c r="B28">
-        <v>0.1118439291180581</v>
+        <v>0.1078639793413442</v>
       </c>
       <c r="C28">
-        <v>0.1154267389388929</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D28">
-        <v>0.1183140898411064</v>
+        <v>0.1155228501683777</v>
       </c>
       <c r="E28">
-        <v>0.1212059488290073</v>
+        <v>0.1183950445613753</v>
       </c>
       <c r="F28">
-        <v>0.1190978083717598</v>
+        <v>0.1210570713249419</v>
       </c>
       <c r="G28">
-        <v>0.1181615926650469</v>
+        <v>0.1188467090685207</v>
       </c>
       <c r="H28">
-        <v>0.1152019145052329</v>
+        <v>0.1178498749131232</v>
       </c>
       <c r="I28">
-        <v>0.117966770708857</v>
+        <v>0.1168791034352642</v>
       </c>
       <c r="J28">
-        <v>0.1146960052509891</v>
+        <v>0.1202923376175023</v>
       </c>
       <c r="K28">
-        <v>0.1075109501681347</v>
+        <v>0.119034159934109</v>
       </c>
       <c r="L28">
-        <v>0.1003880036585729</v>
+        <v>0.1156517083309323</v>
       </c>
       <c r="M28">
-        <v>0.09829045524953356</v>
+        <v>0.1027260768629837</v>
       </c>
       <c r="N28">
-        <v>0.09992608071955363</v>
+        <v>9.9921335803130062E-2</v>
       </c>
       <c r="O28">
-        <v>0.1034379751701014</v>
+        <v>9.8039729322197885E-2</v>
       </c>
       <c r="P28">
-        <v>0.1069224063235911</v>
+        <v>9.7407405016103468E-2</v>
       </c>
       <c r="Q28">
-        <v>0.111660925659889</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>9.7168897117856576E-2</v>
+      </c>
+      <c r="R28">
+        <v>9.7713847245056162E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>45</v>
       </c>
       <c r="B29">
-        <v>0.112182964344413</v>
+        <v>0.10534320203489719</v>
       </c>
       <c r="C29">
-        <v>0.1158967097699677</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D29">
-        <v>0.1187973228235217</v>
+        <v>0.1157097380288922</v>
       </c>
       <c r="E29">
-        <v>0.1218626384619392</v>
+        <v>0.1187669375724224</v>
       </c>
       <c r="F29">
-        <v>0.1194540305676368</v>
+        <v>0.12171800351177239</v>
       </c>
       <c r="G29">
-        <v>0.1182420281942268</v>
+        <v>0.11949043966270929</v>
       </c>
       <c r="H29">
-        <v>0.1171705618588285</v>
+        <v>0.1182648287083061</v>
       </c>
       <c r="I29">
-        <v>0.1219360608915472</v>
+        <v>0.11711446778000451</v>
       </c>
       <c r="J29">
-        <v>0.1183159999067883</v>
+        <v>0.1205572349283193</v>
       </c>
       <c r="K29">
-        <v>0.1141089444544935</v>
+        <v>0.1191595220559326</v>
       </c>
       <c r="L29">
-        <v>0.102381941819309</v>
+        <v>0.1157786745576536</v>
       </c>
       <c r="M29">
-        <v>0.1004176447862033</v>
+        <v>0.1036379003967851</v>
       </c>
       <c r="N29">
-        <v>0.09914551412548524</v>
+        <v>0.10038566676255239</v>
       </c>
       <c r="O29">
-        <v>0.1007898034997671</v>
+        <v>9.7735853860065072E-2</v>
       </c>
       <c r="P29">
-        <v>0.1039370982387769</v>
+        <v>9.6827578642122103E-2</v>
       </c>
       <c r="Q29">
-        <v>0.1077534497882048</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>9.6201097689487161E-2</v>
+      </c>
+      <c r="R29">
+        <v>9.5430200233689644E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>46</v>
       </c>
       <c r="B30">
-        <v>0.1150990755704579</v>
+        <v>0.10643979546896</v>
       </c>
       <c r="C30">
-        <v>0.1156924776485568</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D30">
-        <v>0.118904695344818</v>
+        <v>0.115854151599335</v>
       </c>
       <c r="E30">
-        <v>0.119578073623398</v>
+        <v>0.11884772560428181</v>
       </c>
       <c r="F30">
-        <v>0.1163869645347033</v>
+        <v>0.1213164406780203</v>
       </c>
       <c r="G30">
-        <v>0.1189013233679165</v>
+        <v>0.1191496283553603</v>
       </c>
       <c r="H30">
-        <v>0.1169439141675783</v>
+        <v>0.1180058818756488</v>
       </c>
       <c r="I30">
-        <v>0.1114245232661569</v>
+        <v>0.11700812192610489</v>
       </c>
       <c r="J30">
-        <v>0.1147518081186082</v>
+        <v>0.1201859293985373</v>
       </c>
       <c r="K30">
-        <v>0.1070024757041417</v>
+        <v>0.1184563471984328</v>
       </c>
       <c r="L30">
-        <v>0.1016515070638637</v>
+        <v>0.115766004903884</v>
       </c>
       <c r="M30">
-        <v>0.1005785851829374</v>
+        <v>0.10370705975805281</v>
       </c>
       <c r="N30">
-        <v>0.1017663320222195</v>
+        <v>0.1003093863643391</v>
       </c>
       <c r="O30">
-        <v>0.103963627058528</v>
+        <v>9.7925026897963466E-2</v>
       </c>
       <c r="P30">
-        <v>0.1078250105978348</v>
+        <v>9.6600059124120743E-2</v>
       </c>
       <c r="Q30">
-        <v>0.11268611575876</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>9.5447170126730846E-2</v>
+      </c>
+      <c r="R30">
+        <v>9.4728661827965646E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>47</v>
       </c>
       <c r="B31">
-        <v>0.1036086989193432</v>
+        <v>0.1065521433445837</v>
       </c>
       <c r="C31">
-        <v>0.1157199146216567</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D31">
-        <v>0.1192847156638752</v>
+        <v>0.1154380817369471</v>
       </c>
       <c r="E31">
-        <v>0.1200404069921582</v>
+        <v>0.11809624199990559</v>
       </c>
       <c r="F31">
-        <v>0.1169556106750421</v>
+        <v>0.120975247813305</v>
       </c>
       <c r="G31">
-        <v>0.1187906861028112</v>
+        <v>0.1186880784707306</v>
       </c>
       <c r="H31">
-        <v>0.117385534005902</v>
+        <v>0.11772115048526779</v>
       </c>
       <c r="I31">
-        <v>0.111854489729837</v>
+        <v>0.1167327172479098</v>
       </c>
       <c r="J31">
-        <v>0.1157678520378181</v>
+        <v>0.1201572646475212</v>
       </c>
       <c r="K31">
-        <v>0.1088691004283903</v>
+        <v>0.1195537283258389</v>
       </c>
       <c r="L31">
-        <v>0.1006831379409446</v>
+        <v>0.11682881477700729</v>
       </c>
       <c r="M31">
-        <v>0.09687284231019021</v>
+        <v>0.1052552764300858</v>
       </c>
       <c r="N31">
-        <v>0.09454640688499748</v>
+        <v>0.10182069911995641</v>
       </c>
       <c r="O31">
-        <v>0.09357248116325492</v>
+        <v>9.9842561744339142E-2</v>
       </c>
       <c r="P31">
-        <v>0.09549307174008538</v>
+        <v>9.7622705666795609E-2</v>
       </c>
       <c r="Q31">
-        <v>0.09576321471609726</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-        </is>
+        <v>9.6753834866186494E-2</v>
+      </c>
+      <c r="R31">
+        <v>9.5391427478880894E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>48</v>
       </c>
       <c r="B32">
-        <v>0.1079857491041191</v>
+        <v>0.10708659106605289</v>
       </c>
       <c r="C32">
-        <v>0.115712141868659</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D32">
-        <v>0.1185256681425094</v>
+        <v>0.1155044702074092</v>
       </c>
       <c r="E32">
-        <v>0.1214367474405629</v>
+        <v>0.11855056606642771</v>
       </c>
       <c r="F32">
-        <v>0.1190737629743409</v>
+        <v>0.1214646439352414</v>
       </c>
       <c r="G32">
-        <v>0.1180450709216662</v>
+        <v>0.1191628102905553</v>
       </c>
       <c r="H32">
-        <v>0.1172374467054416</v>
+        <v>0.1178561587547144</v>
       </c>
       <c r="I32">
-        <v>0.1207386297098142</v>
+        <v>0.11657857387928081</v>
       </c>
       <c r="J32">
-        <v>0.1191295515257424</v>
+        <v>0.1199109786876509</v>
       </c>
       <c r="K32">
-        <v>0.1157391574079969</v>
+        <v>0.1181635158547636</v>
       </c>
       <c r="L32">
-        <v>0.1040716985785074</v>
+        <v>0.11473709010956221</v>
       </c>
       <c r="M32">
-        <v>0.100496888475318</v>
+        <v>0.1018203263534921</v>
       </c>
       <c r="N32">
-        <v>0.0986618733998626</v>
+        <v>9.9270812888538992E-2</v>
       </c>
       <c r="O32">
-        <v>0.09728873123028042</v>
+        <v>9.7714437300776905E-2</v>
       </c>
       <c r="P32">
-        <v>0.09739241772465324</v>
+        <v>9.7683444181191126E-2</v>
       </c>
       <c r="Q32">
-        <v>0.09728509770970913</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-        </is>
+        <v>9.8520782719623043E-2</v>
+      </c>
+      <c r="R32">
+        <v>9.933266557815365E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>49</v>
       </c>
       <c r="B33">
-        <v>0.1051624165606507</v>
+        <v>0.1083586230560649</v>
       </c>
       <c r="C33">
-        <v>0.1158095650188834</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D33">
-        <v>0.1187934511595916</v>
+        <v>0.11582756907989809</v>
       </c>
       <c r="E33">
-        <v>0.1216123547131817</v>
+        <v>0.11895491781416739</v>
       </c>
       <c r="F33">
-        <v>0.1192710406002679</v>
+        <v>0.12176461593983</v>
       </c>
       <c r="G33">
-        <v>0.1181373531826288</v>
+        <v>0.1195796134369848</v>
       </c>
       <c r="H33">
-        <v>0.1167772429822115</v>
+        <v>0.1182098323910471</v>
       </c>
       <c r="I33">
-        <v>0.1201422812660392</v>
+        <v>0.117351875741443</v>
       </c>
       <c r="J33">
-        <v>0.1182790135749806</v>
+        <v>0.1207189354103374</v>
       </c>
       <c r="K33">
-        <v>0.1150436655784997</v>
+        <v>0.1190493209084048</v>
       </c>
       <c r="L33">
-        <v>0.1027435926916544</v>
+        <v>0.1157922069122425</v>
       </c>
       <c r="M33">
-        <v>0.09957890790228215</v>
+        <v>0.1037735223336362</v>
       </c>
       <c r="N33">
-        <v>0.09755586270912243</v>
+        <v>0.1007127778117715</v>
       </c>
       <c r="O33">
-        <v>0.09612665651850538</v>
+        <v>9.8917841683235766E-2</v>
       </c>
       <c r="P33">
-        <v>0.09535431450386847</v>
+        <v>9.8373360568640295E-2</v>
       </c>
       <c r="Q33">
-        <v>0.0949520320762112</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-        </is>
+        <v>9.8845269949422943E-2</v>
+      </c>
+      <c r="R33">
+        <v>9.9581094859724675E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>50</v>
       </c>
       <c r="B34">
-        <v>0.1052434209119581</v>
+        <v>0.1090088169362744</v>
       </c>
       <c r="C34">
-        <v>0.1155077947402629</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D34">
-        <v>0.1184709610947524</v>
+        <v>0.1157282156173385</v>
       </c>
       <c r="E34">
-        <v>0.1214860685845777</v>
+        <v>0.1189607131436744</v>
       </c>
       <c r="F34">
-        <v>0.1192984766199852</v>
+        <v>0.12183203572925</v>
       </c>
       <c r="G34">
-        <v>0.117848646817709</v>
+        <v>0.119362284876405</v>
       </c>
       <c r="H34">
-        <v>0.1166856343788837</v>
+        <v>0.1183301489578398</v>
       </c>
       <c r="I34">
-        <v>0.1202327949039949</v>
+        <v>0.1172633682760767</v>
       </c>
       <c r="J34">
-        <v>0.1189124384912526</v>
+        <v>0.12093972119630381</v>
       </c>
       <c r="K34">
-        <v>0.1159183702962381</v>
+        <v>0.1188949329156261</v>
       </c>
       <c r="L34">
-        <v>0.1042390966912859</v>
+        <v>0.1157636830522045</v>
       </c>
       <c r="M34">
-        <v>0.1006259226093117</v>
+        <v>0.1048473515685075</v>
       </c>
       <c r="N34">
-        <v>0.09834603418602222</v>
+        <v>0.1013942663053736</v>
       </c>
       <c r="O34">
-        <v>0.0972728615711774</v>
+        <v>9.9500065018896341E-2</v>
       </c>
       <c r="P34">
-        <v>0.09621953847857381</v>
+        <v>9.826225713088671E-2</v>
       </c>
       <c r="Q34">
-        <v>0.0957689058127587</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-        </is>
+        <v>9.8232152135205586E-2</v>
+      </c>
+      <c r="R34">
+        <v>9.8833832637502242E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>51</v>
       </c>
       <c r="B35">
-        <v>0.1075309586745763</v>
+        <v>0.1090626460652008</v>
       </c>
       <c r="C35">
-        <v>0.1156755190569699</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D35">
-        <v>0.1188454893615852</v>
+        <v>0.1157259154416011</v>
       </c>
       <c r="E35">
-        <v>0.1217624422912262</v>
+        <v>0.118472736126836</v>
       </c>
       <c r="F35">
-        <v>0.1195472632765321</v>
+        <v>0.1212438167311455</v>
       </c>
       <c r="G35">
-        <v>0.1184661806824905</v>
+        <v>0.1190515904432215</v>
       </c>
       <c r="H35">
-        <v>0.1174645873102733</v>
+        <v>0.11794013756654979</v>
       </c>
       <c r="I35">
-        <v>0.1210673408731778</v>
+        <v>0.11699103839193049</v>
       </c>
       <c r="J35">
-        <v>0.1201227865939377</v>
+        <v>0.1208145464760409</v>
       </c>
       <c r="K35">
-        <v>0.117493562061928</v>
+        <v>0.1194759332495901</v>
       </c>
       <c r="L35">
-        <v>0.1065997278345096</v>
+        <v>0.11623599289686121</v>
       </c>
       <c r="M35">
-        <v>0.1025544429524453</v>
+        <v>0.10392513352168679</v>
       </c>
       <c r="N35">
-        <v>0.1001807233941542</v>
+        <v>0.10119864185797919</v>
       </c>
       <c r="O35">
-        <v>0.09799335232472631</v>
+        <v>9.9000173073253137E-2</v>
       </c>
       <c r="P35">
-        <v>0.09713878249541301</v>
+        <v>9.8238568114030547E-2</v>
       </c>
       <c r="Q35">
-        <v>0.09541912979468949</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>9.8310750298431115E-2</v>
+      </c>
+      <c r="R35">
+        <v>9.8240792537470423E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>52</v>
       </c>
       <c r="B36">
-        <v>0.1086242922620971</v>
+        <v>0.10793810865099571</v>
       </c>
       <c r="C36">
-        <v>0.1159040654289855</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D36">
-        <v>0.119256868148777</v>
+        <v>0.1157571304705831</v>
       </c>
       <c r="E36">
-        <v>0.1219031602760272</v>
+        <v>0.1188483935450978</v>
       </c>
       <c r="F36">
-        <v>0.1194023712695145</v>
+        <v>0.1213403752090928</v>
       </c>
       <c r="G36">
-        <v>0.1185231364868593</v>
+        <v>0.1192013755659535</v>
       </c>
       <c r="H36">
-        <v>0.1175523780838365</v>
+        <v>0.1181139580923856</v>
       </c>
       <c r="I36">
-        <v>0.1216556668661609</v>
+        <v>0.11713976698656189</v>
       </c>
       <c r="J36">
-        <v>0.1191465706115753</v>
+        <v>0.12031547478198169</v>
       </c>
       <c r="K36">
-        <v>0.1156914654576128</v>
+        <v>0.1188771078293387</v>
       </c>
       <c r="L36">
-        <v>0.1030125024673381</v>
+        <v>0.1162311044328552</v>
       </c>
       <c r="M36">
-        <v>0.1000805240202844</v>
+        <v>0.10593249017669119</v>
       </c>
       <c r="N36">
-        <v>0.09759239996514293</v>
+        <v>0.1013882469126695</v>
       </c>
       <c r="O36">
-        <v>0.09705447906015874</v>
+        <v>9.9854867383549234E-2</v>
       </c>
       <c r="P36">
-        <v>0.09781734338342866</v>
+        <v>9.7495703948726142E-2</v>
       </c>
       <c r="Q36">
-        <v>0.09893671451472287</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-        </is>
+        <v>9.6716073862838273E-2</v>
+      </c>
+      <c r="R36">
+        <v>9.4850231362297366E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>53</v>
       </c>
       <c r="B37">
-        <v>0.1075207412446563</v>
+        <v>0.1195484345397769</v>
       </c>
       <c r="C37">
-        <v>0.1154936391058342</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D37">
-        <v>0.1183026110819424</v>
+        <v>0.1183327416305613</v>
       </c>
       <c r="E37">
-        <v>0.120996712499822</v>
+        <v>0.12231128641207389</v>
       </c>
       <c r="F37">
-        <v>0.1189129028450121</v>
+        <v>0.11844752113463509</v>
       </c>
       <c r="G37">
-        <v>0.1175392009936833</v>
+        <v>0.11368367978258451</v>
       </c>
       <c r="H37">
-        <v>0.116696098821001</v>
+        <v>0.1173173298063505</v>
       </c>
       <c r="I37">
-        <v>0.1201657849610731</v>
+        <v>0.11425719055873459</v>
       </c>
       <c r="J37">
-        <v>0.1184854087519595</v>
+        <v>0.1091921020926483</v>
       </c>
       <c r="K37">
-        <v>0.1152360650912509</v>
+        <v>0.10708346356282181</v>
       </c>
       <c r="L37">
-        <v>0.1028492483164958</v>
+        <v>0.1074079522815387</v>
       </c>
       <c r="M37">
-        <v>0.1000161705156483</v>
+        <v>0.1070329549323816</v>
       </c>
       <c r="N37">
-        <v>0.09786174740668883</v>
+        <v>0.10762761625834839</v>
       </c>
       <c r="O37">
-        <v>0.0976407108550446</v>
+        <v>0.1100654273916586</v>
       </c>
       <c r="P37">
-        <v>0.09790689898696883</v>
+        <v>0.10874781557496151</v>
       </c>
       <c r="Q37">
-        <v>0.09910904017236238</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-        </is>
+        <v>0.1087051639697353</v>
+      </c>
+      <c r="R37">
+        <v>0.10865203530403809</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>54</v>
       </c>
       <c r="B38">
-        <v>0.1076372714914676</v>
+        <v>0.1035783457621379</v>
       </c>
       <c r="C38">
-        <v>0.1157032202041617</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D38">
-        <v>0.1186737013317057</v>
+        <v>0.11688858906156829</v>
       </c>
       <c r="E38">
-        <v>0.1213677576651504</v>
+        <v>0.1212365018643663</v>
       </c>
       <c r="F38">
-        <v>0.1187744849078506</v>
+        <v>0.1196734325606402</v>
       </c>
       <c r="G38">
-        <v>0.1176226809828683</v>
+        <v>0.1116037225209847</v>
       </c>
       <c r="H38">
-        <v>0.1164258675508077</v>
+        <v>0.1102012842979256</v>
       </c>
       <c r="I38">
-        <v>0.1195761091002873</v>
+        <v>0.1029804868616797</v>
       </c>
       <c r="J38">
-        <v>0.1181775546797815</v>
+        <v>9.5246756419065229E-2</v>
       </c>
       <c r="K38">
-        <v>0.114892887077763</v>
+        <v>9.5350082095608815E-2</v>
       </c>
       <c r="L38">
-        <v>0.1031036846179422</v>
+        <v>9.7802565193118834E-2</v>
       </c>
       <c r="M38">
-        <v>0.1001464656542668</v>
+        <v>0.10021220605491291</v>
       </c>
       <c r="N38">
-        <v>0.09818707567278864</v>
+        <v>0.1005706711082644</v>
       </c>
       <c r="O38">
-        <v>0.09742171941048061</v>
+        <v>0.10122555770121031</v>
       </c>
       <c r="P38">
-        <v>0.09682474231175439</v>
+        <v>0.1010685294520564</v>
       </c>
       <c r="Q38">
-        <v>0.09812160466439174</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.1001505330342036</v>
+      </c>
+      <c r="R38">
+        <v>9.9629838538216484E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>55</v>
       </c>
       <c r="B39">
-        <v>0.1080998777996955</v>
+        <v>0.1060328019866742</v>
       </c>
       <c r="C39">
-        <v>0.1158204979711369</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D39">
-        <v>0.1189115827258922</v>
+        <v>0.1166170249972721</v>
       </c>
       <c r="E39">
-        <v>0.121639982090325</v>
+        <v>0.1204974777614666</v>
       </c>
       <c r="F39">
-        <v>0.1194317317823492</v>
+        <v>0.1184093007578297</v>
       </c>
       <c r="G39">
-        <v>0.1180019852499875</v>
+        <v>0.11146149454794781</v>
       </c>
       <c r="H39">
-        <v>0.1170899777665157</v>
+        <v>0.1112993390828092</v>
       </c>
       <c r="I39">
-        <v>0.1205674761974236</v>
+        <v>0.104960074241915</v>
       </c>
       <c r="J39">
-        <v>0.1188593812894216</v>
+        <v>9.724389388364911E-2</v>
       </c>
       <c r="K39">
-        <v>0.1155329324297596</v>
+        <v>9.7770681422474165E-2</v>
       </c>
       <c r="L39">
-        <v>0.1037282543458348</v>
+        <v>9.7210024481273721E-2</v>
       </c>
       <c r="M39">
-        <v>0.1009324984177762</v>
+        <v>9.7671456952657804E-2</v>
       </c>
       <c r="N39">
-        <v>0.09862472903316867</v>
+        <v>9.8849471908683928E-2</v>
       </c>
       <c r="O39">
-        <v>0.09795676707036652</v>
+        <v>9.749637843697577E-2</v>
       </c>
       <c r="P39">
-        <v>0.09766299370552278</v>
+        <v>9.8529003075246813E-2</v>
       </c>
       <c r="Q39">
-        <v>0.09849489385466223</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>9.9335753873602786E-2</v>
+      </c>
+      <c r="R39">
+        <v>9.8969866848868618E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>56</v>
       </c>
       <c r="B40">
-        <v>0.1067023461957979</v>
+        <v>0.1172110678075253</v>
       </c>
       <c r="C40">
-        <v>0.1157957218916988</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D40">
-        <v>0.1187063293965262</v>
+        <v>0.1177261778601524</v>
       </c>
       <c r="E40">
-        <v>0.1213163181493526</v>
+        <v>0.11618647417079229</v>
       </c>
       <c r="F40">
-        <v>0.1190708733906743</v>
+        <v>0.1119643250494341</v>
       </c>
       <c r="G40">
-        <v>0.1180073286520164</v>
+        <v>0.11332894024667919</v>
       </c>
       <c r="H40">
-        <v>0.116943379477371</v>
+        <v>0.1064125971596927</v>
       </c>
       <c r="I40">
-        <v>0.1202283264284908</v>
+        <v>0.1027654642063377</v>
       </c>
       <c r="J40">
-        <v>0.1187869057334296</v>
+        <v>0.1027551580605041</v>
       </c>
       <c r="K40">
-        <v>0.1158213544461456</v>
+        <v>0.10512171760652519</v>
       </c>
       <c r="L40">
-        <v>0.1050159254101412</v>
+        <v>0.1049896556358484</v>
       </c>
       <c r="M40">
-        <v>0.1012902458999878</v>
+        <v>0.1028086590309651</v>
       </c>
       <c r="N40">
-        <v>0.09928645726414918</v>
+        <v>0.10325615101311519</v>
       </c>
       <c r="O40">
-        <v>0.09725120252405259</v>
+        <v>0.1021352542058514</v>
       </c>
       <c r="P40">
-        <v>0.09639528326119116</v>
+        <v>0.1031501199929739</v>
       </c>
       <c r="Q40">
-        <v>0.09457998683228701</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.1049280512462112</v>
+      </c>
+      <c r="R40">
+        <v>0.1086699031616726</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>57</v>
       </c>
       <c r="B41">
-        <v>0.1203411726060178</v>
+        <v>0.1183939615298254</v>
       </c>
       <c r="C41">
-        <v>0.1180777265140174</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D41">
-        <v>0.1218177429455499</v>
+        <v>0.11826959533494349</v>
       </c>
       <c r="E41">
-        <v>0.1183648666451378</v>
+        <v>0.12592848529298861</v>
       </c>
       <c r="F41">
-        <v>0.1136024368931457</v>
+        <v>0.12122807271517309</v>
       </c>
       <c r="G41">
-        <v>0.1168787859025793</v>
+        <v>0.12108194687038749</v>
       </c>
       <c r="H41">
-        <v>0.1140703742606337</v>
+        <v>0.11676840830926941</v>
       </c>
       <c r="I41">
-        <v>0.1086807346558239</v>
+        <v>0.1158562369296436</v>
       </c>
       <c r="J41">
-        <v>0.1065376570574061</v>
+        <v>0.1142933392317569</v>
       </c>
       <c r="K41">
-        <v>0.1068477269564636</v>
+        <v>0.1116813423787326</v>
       </c>
       <c r="L41">
-        <v>0.1063735276996065</v>
+        <v>0.11378444885544479</v>
       </c>
       <c r="M41">
-        <v>0.1073778400511941</v>
+        <v>0.1153964917224045</v>
       </c>
       <c r="N41">
-        <v>0.1097960580325194</v>
+        <v>0.1154791235609606</v>
       </c>
       <c r="O41">
-        <v>0.108545998052558</v>
+        <v>0.11661595021680191</v>
       </c>
       <c r="P41">
-        <v>0.1083721541503955</v>
+        <v>0.1193855289177622</v>
       </c>
       <c r="Q41">
-        <v>0.1083970237198404</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-        </is>
+        <v>0.11973510360733471</v>
+      </c>
+      <c r="R41">
+        <v>0.1204554720906916</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>58</v>
       </c>
       <c r="B42">
-        <v>0.1043731368526334</v>
+        <v>0.1068112328529485</v>
       </c>
       <c r="C42">
-        <v>0.1165643448061762</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D42">
-        <v>0.120941320660191</v>
+        <v>0.1132781852425202</v>
       </c>
       <c r="E42">
-        <v>0.1194952659908395</v>
+        <v>0.1285213936045628</v>
       </c>
       <c r="F42">
-        <v>0.1115326654366049</v>
+        <v>0.12237326208505921</v>
       </c>
       <c r="G42">
-        <v>0.1103555201648455</v>
+        <v>0.1092213511077231</v>
       </c>
       <c r="H42">
-        <v>0.1030523656388864</v>
+        <v>0.10479109859705329</v>
       </c>
       <c r="I42">
-        <v>0.09566067181443408</v>
+        <v>0.1017724392643653</v>
       </c>
       <c r="J42">
-        <v>0.09578398150347799</v>
+        <v>9.6395489824880456E-2</v>
       </c>
       <c r="K42">
-        <v>0.09843937907419126</v>
+        <v>9.5664090345589009E-2</v>
       </c>
       <c r="L42">
-        <v>0.1011826412300454</v>
+        <v>9.7094222743773315E-2</v>
       </c>
       <c r="M42">
-        <v>0.1014551828401483</v>
+        <v>9.5643015561415287E-2</v>
       </c>
       <c r="N42">
-        <v>0.1022694446896126</v>
+        <v>9.5826955399479483E-2</v>
       </c>
       <c r="O42">
-        <v>0.1017719779877868</v>
+        <v>9.6937016280570082E-2</v>
       </c>
       <c r="P42">
-        <v>0.1005915761860742</v>
+        <v>9.7424602079681039E-2</v>
       </c>
       <c r="Q42">
-        <v>0.09985753212969693</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>9.7089746805650148E-2</v>
+      </c>
+      <c r="R42">
+        <v>9.8186756622749977E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>59</v>
       </c>
       <c r="B43">
-        <v>0.1067686256152511</v>
+        <v>0.1060287226691259</v>
       </c>
       <c r="C43">
-        <v>0.1166488210060977</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D43">
-        <v>0.1202677963984483</v>
+        <v>0.1157773059681165</v>
       </c>
       <c r="E43">
-        <v>0.1181804758781907</v>
+        <v>0.11815387164177669</v>
       </c>
       <c r="F43">
-        <v>0.1119656350729256</v>
+        <v>0.11247605171897131</v>
       </c>
       <c r="G43">
-        <v>0.111344816316402</v>
+        <v>0.11037131284996129</v>
       </c>
       <c r="H43">
-        <v>0.1053801603033712</v>
+        <v>0.101422318512275</v>
       </c>
       <c r="I43">
-        <v>0.09715855828241755</v>
+        <v>9.8085250132904436E-2</v>
       </c>
       <c r="J43">
-        <v>0.09767400811067797</v>
+        <v>9.6104555756950899E-2</v>
       </c>
       <c r="K43">
-        <v>0.0972007992426261</v>
+        <v>9.6605100761408699E-2</v>
       </c>
       <c r="L43">
-        <v>0.09779345705954656</v>
+        <v>9.8789957503462117E-2</v>
       </c>
       <c r="M43">
-        <v>0.0982825394543185</v>
+        <v>9.6139848239840259E-2</v>
       </c>
       <c r="N43">
-        <v>0.09724373040824913</v>
+        <v>9.5937564339746234E-2</v>
       </c>
       <c r="O43">
-        <v>0.09797302055494858</v>
+        <v>9.5831238215935602E-2</v>
       </c>
       <c r="P43">
-        <v>0.09910735201209227</v>
+        <v>9.6810884172035802E-2</v>
       </c>
       <c r="Q43">
-        <v>0.09873463963269898</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.1160694160121382</v>
-      </c>
-      <c r="C44">
-        <v>0.1182821548742386</v>
-      </c>
-      <c r="D44">
-        <v>0.1166236874100363</v>
-      </c>
-      <c r="E44">
-        <v>0.1116838435030778</v>
-      </c>
-      <c r="F44">
-        <v>0.1134066400728571</v>
-      </c>
-      <c r="G44">
-        <v>0.1065550195736849</v>
-      </c>
-      <c r="H44">
-        <v>0.1026289176824021</v>
-      </c>
-      <c r="I44">
-        <v>0.1029874396942331</v>
-      </c>
-      <c r="J44">
-        <v>0.1053076596533017</v>
-      </c>
-      <c r="K44">
-        <v>0.1056041755545694</v>
-      </c>
-      <c r="L44">
-        <v>0.1034159334631091</v>
-      </c>
-      <c r="M44">
-        <v>0.1040668456509806</v>
-      </c>
-      <c r="N44">
-        <v>0.1031884197479186</v>
-      </c>
-      <c r="O44">
-        <v>0.1043110924704865</v>
-      </c>
-      <c r="P44">
-        <v>0.1060469353845587</v>
-      </c>
-      <c r="Q44">
-        <v>0.1092057866865437</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.1184501217489028</v>
-      </c>
-      <c r="C45">
-        <v>0.1182876750315514</v>
-      </c>
-      <c r="D45">
-        <v>0.1270062885211053</v>
-      </c>
-      <c r="E45">
-        <v>0.1219633890579051</v>
-      </c>
-      <c r="F45">
-        <v>0.1216990346494259</v>
-      </c>
-      <c r="G45">
-        <v>0.1178517041613216</v>
-      </c>
-      <c r="H45">
-        <v>0.1166554584987256</v>
-      </c>
-      <c r="I45">
-        <v>0.1155806003325335</v>
-      </c>
-      <c r="J45">
-        <v>0.1130979080090069</v>
-      </c>
-      <c r="K45">
-        <v>0.1145281588255732</v>
-      </c>
-      <c r="L45">
-        <v>0.1162958226703595</v>
-      </c>
-      <c r="M45">
-        <v>0.1160880473481839</v>
-      </c>
-      <c r="N45">
-        <v>0.1172218622792674</v>
-      </c>
-      <c r="O45">
-        <v>0.1200628941017145</v>
-      </c>
-      <c r="P45">
-        <v>0.1205106527540746</v>
-      </c>
-      <c r="Q45">
-        <v>0.1215533928498523</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.1064728866010351</v>
-      </c>
-      <c r="C46">
-        <v>0.1130214899866195</v>
-      </c>
-      <c r="D46">
-        <v>0.1275813881540055</v>
-      </c>
-      <c r="E46">
-        <v>0.1207061432456829</v>
-      </c>
-      <c r="F46">
-        <v>0.1080599993306307</v>
-      </c>
-      <c r="G46">
-        <v>0.1042813524143531</v>
-      </c>
-      <c r="H46">
-        <v>0.1015275482094735</v>
-      </c>
-      <c r="I46">
-        <v>0.09619074802278288</v>
-      </c>
-      <c r="J46">
-        <v>0.09567860856139104</v>
-      </c>
-      <c r="K46">
-        <v>0.09670218654371043</v>
-      </c>
-      <c r="L46">
-        <v>0.0952900034761901</v>
-      </c>
-      <c r="M46">
-        <v>0.09565254871852132</v>
-      </c>
-      <c r="N46">
-        <v>0.09700637706902809</v>
-      </c>
-      <c r="O46">
-        <v>0.09728686999769955</v>
-      </c>
-      <c r="P46">
-        <v>0.09727384599784435</v>
-      </c>
-      <c r="Q46">
-        <v>0.0983832218414276</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0.1059783452784343</v>
-      </c>
-      <c r="C47">
-        <v>0.1162936509344983</v>
-      </c>
-      <c r="D47">
-        <v>0.1187724020639986</v>
-      </c>
-      <c r="E47">
-        <v>0.1133724540150501</v>
-      </c>
-      <c r="F47">
-        <v>0.1116135508120838</v>
-      </c>
-      <c r="G47">
-        <v>0.1018080382300647</v>
-      </c>
-      <c r="H47">
-        <v>0.09885484624979204</v>
-      </c>
-      <c r="I47">
-        <v>0.0963308357159251</v>
-      </c>
-      <c r="J47">
-        <v>0.09714198790465997</v>
-      </c>
-      <c r="K47">
-        <v>0.09916427434897307</v>
-      </c>
-      <c r="L47">
-        <v>0.09701201984831469</v>
-      </c>
-      <c r="M47">
-        <v>0.09695021996161288</v>
-      </c>
-      <c r="N47">
-        <v>0.096919604555956</v>
-      </c>
-      <c r="O47">
-        <v>0.09833670611533028</v>
-      </c>
-      <c r="P47">
-        <v>0.09938011854517222</v>
-      </c>
-      <c r="Q47">
-        <v>0.1009401394409097</v>
+        <v>9.8042413219205996E-2</v>
+      </c>
+      <c r="R43">
+        <v>9.9160467291833074E-2</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C2:R43">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>